--- a/12625957.xlsx
+++ b/12625957.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -295,6 +295,15 @@
   </si>
   <si>
     <t>take ride</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>read about dsa</t>
+  </si>
+  <si>
+    <t>prepare for python CA</t>
   </si>
 </sst>
 </file>
@@ -2406,49 +2415,93 @@
       <c r="A35" s="13">
         <v>46278</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="B35" s="14">
+        <v>300</v>
+      </c>
+      <c r="C35" s="14">
+        <v>120</v>
+      </c>
+      <c r="D35" s="14">
+        <v>120</v>
+      </c>
+      <c r="E35" s="14">
+        <v>120</v>
+      </c>
+      <c r="F35" s="14">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14">
+        <v>360</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="13">
         <v>46279</v>
       </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="B36" s="14">
+        <v>300</v>
+      </c>
+      <c r="C36" s="14">
+        <v>60</v>
+      </c>
+      <c r="D36" s="14">
+        <v>60</v>
+      </c>
+      <c r="E36" s="14">
+        <v>60</v>
+      </c>
+      <c r="F36" s="14">
+        <v>200</v>
+      </c>
+      <c r="G36" s="14">
+        <v>4</v>
+      </c>
+      <c r="H36" s="14">
+        <v>120</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="13">

--- a/12625957.xlsx
+++ b/12625957.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -297,13 +297,16 @@
     <t>take ride</t>
   </si>
   <si>
-    <t>medium</t>
-  </si>
-  <si>
     <t>read about dsa</t>
   </si>
   <si>
     <t>prepare for python CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gave python CA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">not much </t>
   </si>
 </sst>
 </file>
@@ -2454,7 +2457,7 @@
         <v>67</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
@@ -2494,62 +2497,106 @@
         <v>49</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="M36" s="16" t="s">
         <v>80</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="13">
         <v>46280</v>
       </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="B37" s="14">
+        <v>360</v>
+      </c>
+      <c r="C37" s="14">
+        <v>90</v>
+      </c>
+      <c r="D37" s="14">
+        <v>180</v>
+      </c>
+      <c r="E37" s="14">
+        <v>120</v>
+      </c>
+      <c r="F37" s="14">
+        <v>250</v>
+      </c>
+      <c r="G37" s="14">
+        <v>5</v>
+      </c>
+      <c r="H37" s="14">
+        <v>90</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="13">
         <v>46281</v>
       </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="B38" s="14">
+        <v>360</v>
+      </c>
+      <c r="C38" s="14">
+        <v>120</v>
+      </c>
+      <c r="D38" s="14">
+        <v>120</v>
+      </c>
+      <c r="E38" s="14">
+        <v>50</v>
+      </c>
+      <c r="F38" s="14">
+        <v>250</v>
+      </c>
+      <c r="G38" s="14">
+        <v>5</v>
+      </c>
+      <c r="H38" s="14">
+        <v>180</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="13">

--- a/12625957.xlsx
+++ b/12625957.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -308,6 +308,18 @@
   <si>
     <t xml:space="preserve">not much </t>
   </si>
+  <si>
+    <t>practice maths topic percentage</t>
+  </si>
+  <si>
+    <t>start to add personal data</t>
+  </si>
+  <si>
+    <t>good vibes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">start learning coding basic </t>
+  </si>
 </sst>
 </file>
 
@@ -316,7 +328,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -397,6 +409,11 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -445,7 +462,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -489,11 +506,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -956,7 +996,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N404"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1110,11 +1150,11 @@
         <v>30</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I72" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J72" si="1">IF(I6="","",1440-I6)</f>
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1132,169 +1172,169 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="13">
-        <v>46250</v>
-      </c>
-      <c r="B7" s="14">
-        <v>480</v>
-      </c>
-      <c r="C7" s="14">
-        <v>120</v>
-      </c>
-      <c r="D7" s="14">
-        <v>180</v>
-      </c>
-      <c r="E7" s="14">
-        <v>240</v>
-      </c>
-      <c r="F7" s="14">
-        <v>0</v>
-      </c>
-      <c r="G7" s="14">
-        <v>0</v>
-      </c>
-      <c r="H7" s="14">
-        <v>120</v>
-      </c>
-      <c r="I7" s="15">
-        <f>IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
-        <v>1140</v>
-      </c>
-      <c r="J7" s="15">
+        <v>46247</v>
+      </c>
+      <c r="B7" s="9">
+        <v>300</v>
+      </c>
+      <c r="C7" s="9">
+        <v>50</v>
+      </c>
+      <c r="D7" s="9">
+        <v>60</v>
+      </c>
+      <c r="E7" s="22">
+        <v>30</v>
+      </c>
+      <c r="F7" s="22">
+        <v>250</v>
+      </c>
+      <c r="G7" s="22">
+        <v>5</v>
+      </c>
+      <c r="H7" s="22">
+        <v>200</v>
+      </c>
+      <c r="I7" s="21">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J7" s="21">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="K7" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="K7" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="L7" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="M7" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>61</v>
+      <c r="M7" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="N7" s="24" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="13">
-        <v>46251</v>
-      </c>
-      <c r="B8" s="14">
-        <v>360</v>
-      </c>
-      <c r="C8" s="14">
+        <v>46248</v>
+      </c>
+      <c r="B8" s="9">
+        <v>300</v>
+      </c>
+      <c r="C8" s="9">
+        <v>90</v>
+      </c>
+      <c r="D8" s="9">
+        <v>90</v>
+      </c>
+      <c r="E8" s="22">
+        <v>50</v>
+      </c>
+      <c r="F8" s="22">
+        <v>300</v>
+      </c>
+      <c r="G8" s="22">
+        <v>6</v>
+      </c>
+      <c r="H8" s="22">
         <v>120</v>
       </c>
-      <c r="D8" s="14">
-        <v>200</v>
-      </c>
-      <c r="E8" s="14">
-        <v>200</v>
-      </c>
-      <c r="F8" s="14">
-        <v>0</v>
-      </c>
-      <c r="G8" s="14">
-        <v>0</v>
-      </c>
-      <c r="H8" s="14">
-        <v>100</v>
-      </c>
-      <c r="I8" s="15">
+      <c r="I8" s="21">
         <f t="shared" si="0"/>
-        <v>980</v>
-      </c>
-      <c r="J8" s="15">
+        <v>950</v>
+      </c>
+      <c r="J8" s="21">
         <f t="shared" si="1"/>
-        <v>460</v>
-      </c>
-      <c r="K8" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="L8" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="M8" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>62</v>
+      <c r="M8" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="N8" s="24" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="13">
-        <v>46252</v>
-      </c>
-      <c r="B9" s="14">
-        <v>300</v>
-      </c>
-      <c r="C9" s="14">
+        <v>46249</v>
+      </c>
+      <c r="B9" s="9">
+        <v>360</v>
+      </c>
+      <c r="C9" s="9">
         <v>120</v>
       </c>
-      <c r="D9" s="14">
-        <v>240</v>
-      </c>
-      <c r="E9" s="14">
-        <v>120</v>
-      </c>
-      <c r="F9" s="14">
-        <v>300</v>
-      </c>
-      <c r="G9" s="14">
-        <v>6</v>
-      </c>
-      <c r="H9" s="14">
-        <v>120</v>
-      </c>
-      <c r="I9" s="15">
+      <c r="D9" s="9">
+        <v>60</v>
+      </c>
+      <c r="E9" s="22">
+        <v>90</v>
+      </c>
+      <c r="F9" s="22">
+        <v>250</v>
+      </c>
+      <c r="G9" s="22">
+        <v>5</v>
+      </c>
+      <c r="H9" s="22">
+        <v>90</v>
+      </c>
+      <c r="I9" s="21">
         <f t="shared" si="0"/>
-        <v>1200</v>
-      </c>
-      <c r="J9" s="15">
+        <v>970</v>
+      </c>
+      <c r="J9" s="21">
         <f t="shared" si="1"/>
-        <v>240</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M9" s="16" t="s">
+        <v>470</v>
+      </c>
+      <c r="K9" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="N9" s="17" t="s">
-        <v>61</v>
+      <c r="M9" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="24" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="13">
-        <v>46253</v>
+        <v>46250</v>
       </c>
       <c r="B10" s="14">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="C10" s="14">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="D10" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="E10" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="F10" s="14">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G10" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H10" s="14">
         <v>120</v>
       </c>
       <c r="I10" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
         <v>1080</v>
       </c>
       <c r="J10" s="15">
@@ -1305,18 +1345,18 @@
         <v>49</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="13">
-        <v>46254</v>
+        <v>46251</v>
       </c>
       <c r="B11" s="14">
         <v>360</v>
@@ -1325,56 +1365,56 @@
         <v>120</v>
       </c>
       <c r="D11" s="14">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="E11" s="14">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="F11" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G11" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H11" s="14">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>980</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>460</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="M11" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="13">
-        <v>46255</v>
+        <v>46252</v>
       </c>
       <c r="B12" s="14">
         <v>300</v>
       </c>
       <c r="C12" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D12" s="14">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="E12" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="F12" s="14">
         <v>300</v>
@@ -1383,15 +1423,15 @@
         <v>6</v>
       </c>
       <c r="H12" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>1200</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>49</v>
@@ -1400,231 +1440,231 @@
         <v>50</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="13">
-        <v>46256</v>
+        <v>46253</v>
       </c>
       <c r="B13" s="14">
-        <v>420</v>
+        <v>300</v>
       </c>
       <c r="C13" s="14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D13" s="14">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="E13" s="14">
         <v>120</v>
       </c>
       <c r="F13" s="14">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="G13" s="14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H13" s="14">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>1080</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="M13" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="13">
-        <v>46257</v>
+        <v>46254</v>
       </c>
       <c r="B14" s="14">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="C14" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D14" s="14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E14" s="14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F14" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G14" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H14" s="14">
         <v>180</v>
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1200</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>240</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="13">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="B15" s="14">
-        <v>420</v>
+        <v>300</v>
       </c>
       <c r="C15" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D15" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="E15" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="F15" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H15" s="14">
         <v>180</v>
       </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>1100</v>
+        <v>1140</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="13">
-        <v>46259</v>
+        <v>46256</v>
       </c>
       <c r="B16" s="14">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="C16" s="14">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D16" s="14">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="E16" s="14">
         <v>120</v>
       </c>
       <c r="F16" s="14">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H16" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>1140</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="13">
-        <v>46260</v>
+        <v>46257</v>
       </c>
       <c r="B17" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C17" s="14">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D17" s="14">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E17" s="14">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="F17" s="14">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G17" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H17" s="14">
         <v>180</v>
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>1120</v>
+        <v>960</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>480</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="L17" s="16" t="s">
         <v>50</v>
@@ -1633,64 +1673,64 @@
         <v>67</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="13">
-        <v>46261</v>
+        <v>46258</v>
       </c>
       <c r="B18" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C18" s="14">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D18" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E18" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F18" s="14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H18" s="14">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>1170</v>
+        <v>1100</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>270</v>
+        <v>340</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="L18" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M18" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="M18" s="16" t="s">
-        <v>71</v>
-      </c>
       <c r="N18" s="17" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="13">
-        <v>46262</v>
+        <v>46259</v>
       </c>
       <c r="B19" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="C19" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D19" s="14">
         <v>120</v>
@@ -1699,84 +1739,84 @@
         <v>120</v>
       </c>
       <c r="F19" s="14">
+        <v>250</v>
+      </c>
+      <c r="G19" s="14">
+        <v>5</v>
+      </c>
+      <c r="H19" s="14">
         <v>200</v>
-      </c>
-      <c r="G19" s="14">
-        <v>4</v>
-      </c>
-      <c r="H19" s="14">
-        <v>360</v>
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>1220</v>
+        <v>1080</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>360</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="13">
-        <v>46263</v>
+        <v>46260</v>
       </c>
       <c r="B20" s="14">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="C20" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>120</v>
+      </c>
+      <c r="F20" s="14">
+        <v>250</v>
+      </c>
+      <c r="G20" s="14">
+        <v>5</v>
+      </c>
+      <c r="H20" s="14">
         <v>180</v>
-      </c>
-      <c r="E20" s="14">
-        <v>240</v>
-      </c>
-      <c r="F20" s="14">
-        <v>0</v>
-      </c>
-      <c r="G20" s="14">
-        <v>0</v>
-      </c>
-      <c r="H20" s="14">
-        <v>120</v>
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>1120</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>320</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="L20" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="13">
-        <v>46264</v>
+        <v>46261</v>
       </c>
       <c r="B21" s="14">
         <v>360</v>
@@ -1785,30 +1825,30 @@
         <v>90</v>
       </c>
       <c r="D21" s="14">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="E21" s="14">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="F21" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G21" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H21" s="14">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>1070</v>
+        <v>1170</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>370</v>
+        <v>270</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="L21" s="16" t="s">
         <v>65</v>
@@ -1817,41 +1857,41 @@
         <v>71</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="13">
-        <v>46265</v>
+        <v>46262</v>
       </c>
       <c r="B22" s="14">
         <v>360</v>
       </c>
       <c r="C22" s="14">
+        <v>60</v>
+      </c>
+      <c r="D22" s="14">
         <v>120</v>
-      </c>
-      <c r="D22" s="14">
-        <v>200</v>
       </c>
       <c r="E22" s="14">
         <v>120</v>
       </c>
       <c r="F22" s="14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G22" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H22" s="14">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>1400</v>
+        <v>1220</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>220</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>49</v>
@@ -1860,7 +1900,7 @@
         <v>50</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="N22" s="17" t="s">
         <v>62</v>
@@ -1868,36 +1908,36 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="13">
-        <v>46266</v>
+        <v>46263</v>
       </c>
       <c r="B23" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C23" s="14">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D23" s="14">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="E23" s="14">
         <v>240</v>
       </c>
       <c r="F23" s="14">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G23" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H23" s="14">
         <v>120</v>
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>1410</v>
+        <v>1020</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>420</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>49</v>
@@ -1906,7 +1946,7 @@
         <v>50</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="N23" s="17" t="s">
         <v>62</v>
@@ -1914,82 +1954,82 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="13">
-        <v>46267</v>
+        <v>46264</v>
       </c>
       <c r="B24" s="14">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="C24" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D24" s="14">
+        <v>180</v>
+      </c>
+      <c r="E24" s="14">
+        <v>200</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
         <v>240</v>
-      </c>
-      <c r="E24" s="14">
-        <v>0</v>
-      </c>
-      <c r="F24" s="14">
-        <v>300</v>
-      </c>
-      <c r="G24" s="14">
-        <v>6</v>
-      </c>
-      <c r="H24" s="14">
-        <v>60</v>
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>1120</v>
+        <v>1070</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>370</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="13">
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="B25" s="14">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C25" s="14">
         <v>120</v>
       </c>
       <c r="D25" s="14">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="E25" s="14">
         <v>120</v>
       </c>
       <c r="F25" s="14">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G25" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H25" s="14">
-        <v>90</v>
+        <v>300</v>
       </c>
       <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v>1040</v>
+        <v>1400</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>49</v>
@@ -1998,7 +2038,7 @@
         <v>50</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="N25" s="17" t="s">
         <v>62</v>
@@ -2006,7 +2046,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="13">
-        <v>46269</v>
+        <v>46266</v>
       </c>
       <c r="B26" s="14">
         <v>360</v>
@@ -2015,10 +2055,10 @@
         <v>90</v>
       </c>
       <c r="D26" s="14">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="E26" s="14">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="F26" s="14">
         <v>350</v>
@@ -2027,21 +2067,21 @@
         <v>7</v>
       </c>
       <c r="H26" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v>1130</v>
+        <v>1410</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>30</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="M26" s="16" t="s">
         <v>67</v>
@@ -2052,10 +2092,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="13">
-        <v>46270</v>
+        <v>46267</v>
       </c>
       <c r="B27" s="14">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="C27" s="14">
         <v>120</v>
@@ -2064,90 +2104,90 @@
         <v>240</v>
       </c>
       <c r="E27" s="14">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H27" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>1230</v>
+        <v>1120</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>210</v>
+        <v>320</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="13">
-        <v>46271</v>
+        <v>46268</v>
       </c>
       <c r="B28" s="14">
-        <v>420</v>
+        <v>370</v>
       </c>
       <c r="C28" s="14">
         <v>120</v>
       </c>
       <c r="D28" s="14">
-        <v>300</v>
+        <v>90</v>
       </c>
       <c r="E28" s="14">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="F28" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G28" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>1040</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>400</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L28" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="13">
-        <v>46272</v>
+        <v>46269</v>
       </c>
       <c r="B29" s="14">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="C29" s="14">
         <v>90</v>
@@ -2159,218 +2199,222 @@
         <v>120</v>
       </c>
       <c r="F29" s="14">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G29" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H29" s="14">
         <v>90</v>
       </c>
       <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>1130</v>
       </c>
       <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>310</v>
       </c>
       <c r="K29" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="13">
-        <v>46273</v>
+        <v>46270</v>
       </c>
       <c r="B30" s="14">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="C30" s="14">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D30" s="14">
         <v>240</v>
       </c>
       <c r="E30" s="14">
+        <v>280</v>
+      </c>
+      <c r="F30" s="14">
+        <v>50</v>
+      </c>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="14">
         <v>120</v>
-      </c>
-      <c r="F30" s="14">
-        <v>250</v>
-      </c>
-      <c r="G30" s="14">
-        <v>5</v>
-      </c>
-      <c r="H30" s="14">
-        <v>100</v>
       </c>
       <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v>1110</v>
+        <v>1230</v>
       </c>
       <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v>330</v>
+        <v>210</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="13">
-        <v>46274</v>
+        <v>46271</v>
       </c>
       <c r="B31" s="14">
+        <v>420</v>
+      </c>
+      <c r="C31" s="14">
+        <v>120</v>
+      </c>
+      <c r="D31" s="14">
         <v>300</v>
       </c>
-      <c r="C31" s="14">
-        <v>90</v>
-      </c>
-      <c r="D31" s="14">
-        <v>200</v>
-      </c>
       <c r="E31" s="14">
+        <v>240</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
         <v>120</v>
-      </c>
-      <c r="F31" s="14">
-        <v>250</v>
-      </c>
-      <c r="G31" s="14">
-        <v>5</v>
-      </c>
-      <c r="H31" s="14">
-        <v>90</v>
       </c>
       <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>1200</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>240</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="L31" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M31" s="16" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="13">
-        <v>46275</v>
+        <v>46272</v>
       </c>
       <c r="B32" s="14">
         <v>300</v>
       </c>
       <c r="C32" s="14">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="D32" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E32" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F32" s="14">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="G32" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H32" s="14">
-        <v>300</v>
+        <v>90</v>
       </c>
       <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v>970</v>
+        <v>1020</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v>470</v>
+        <v>420</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="L32" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A33" s="13">
-        <v>46276</v>
+        <v>46273</v>
       </c>
       <c r="B33" s="14">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="C33" s="14">
+        <v>100</v>
+      </c>
+      <c r="D33" s="14">
         <v>240</v>
-      </c>
-      <c r="D33" s="14">
-        <v>90</v>
       </c>
       <c r="E33" s="14">
         <v>120</v>
       </c>
       <c r="F33" s="14">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="G33" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H33" s="14">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I33" s="15">
-        <f>IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
-        <v>1210</v>
+        <f t="shared" si="0"/>
+        <v>1110</v>
+      </c>
+      <c r="J33" s="15">
+        <f t="shared" si="1"/>
+        <v>330</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="M33" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="13">
-        <v>46277</v>
+        <v>46274</v>
       </c>
       <c r="B34" s="14">
         <v>300</v>
@@ -2379,76 +2423,76 @@
         <v>90</v>
       </c>
       <c r="D34" s="14">
+        <v>200</v>
+      </c>
+      <c r="E34" s="14">
         <v>120</v>
       </c>
-      <c r="E34" s="14">
-        <v>60</v>
-      </c>
       <c r="F34" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G34" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H34" s="14">
-        <v>360</v>
+        <v>90</v>
       </c>
       <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v>930</v>
+        <v>1050</v>
       </c>
       <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v>510</v>
+        <v>390</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="13">
-        <v>46278</v>
+        <v>46275</v>
       </c>
       <c r="B35" s="14">
         <v>300</v>
       </c>
       <c r="C35" s="14">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="D35" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E35" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F35" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G35" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>970</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>470</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="L35" s="16" t="s">
         <v>50</v>
@@ -2457,246 +2501,330 @@
         <v>67</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B36" s="14">
+        <v>320</v>
+      </c>
+      <c r="C36" s="14">
+        <v>240</v>
+      </c>
+      <c r="D36" s="14">
+        <v>90</v>
+      </c>
+      <c r="E36" s="14">
+        <v>120</v>
+      </c>
+      <c r="F36" s="14">
+        <v>350</v>
+      </c>
+      <c r="G36" s="14">
+        <v>7</v>
+      </c>
+      <c r="H36" s="14">
+        <v>90</v>
+      </c>
+      <c r="I36" s="15">
+        <f>IF(SUM(B36:F36,H36)=0,"",SUM(B36:F36,H36))</f>
+        <v>1210</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A37" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B37" s="14">
+        <v>300</v>
+      </c>
+      <c r="C37" s="14">
+        <v>90</v>
+      </c>
+      <c r="D37" s="14">
+        <v>120</v>
+      </c>
+      <c r="E37" s="14">
+        <v>60</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>360</v>
+      </c>
+      <c r="I37" s="15">
+        <f t="shared" si="0"/>
+        <v>930</v>
+      </c>
+      <c r="J37" s="15">
+        <f t="shared" si="1"/>
+        <v>510</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A38" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B38" s="14">
+        <v>300</v>
+      </c>
+      <c r="C38" s="14">
+        <v>120</v>
+      </c>
+      <c r="D38" s="14">
+        <v>120</v>
+      </c>
+      <c r="E38" s="14">
+        <v>120</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>360</v>
+      </c>
+      <c r="I38" s="15">
+        <f t="shared" si="0"/>
+        <v>1020</v>
+      </c>
+      <c r="J38" s="15">
+        <f t="shared" si="1"/>
+        <v>420</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A39" s="13">
         <v>46279</v>
       </c>
-      <c r="B36" s="14">
+      <c r="B39" s="14">
         <v>300</v>
       </c>
-      <c r="C36" s="14">
+      <c r="C39" s="14">
         <v>60</v>
       </c>
-      <c r="D36" s="14">
+      <c r="D39" s="14">
         <v>60</v>
       </c>
-      <c r="E36" s="14">
+      <c r="E39" s="14">
         <v>60</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F39" s="14">
         <v>200</v>
       </c>
-      <c r="G36" s="14">
+      <c r="G39" s="14">
         <v>4</v>
       </c>
-      <c r="H36" s="14">
+      <c r="H39" s="14">
         <v>120</v>
       </c>
-      <c r="I36" s="15">
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="J36" s="15">
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
         <v>640</v>
       </c>
-      <c r="K36" s="16" t="s">
+      <c r="K39" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L36" s="16" t="s">
+      <c r="L39" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M36" s="16" t="s">
+      <c r="M39" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="N36" s="17" t="s">
+      <c r="N39" s="17" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="13">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A40" s="13">
         <v>46280</v>
       </c>
-      <c r="B37" s="14">
+      <c r="B40" s="14">
         <v>360</v>
       </c>
-      <c r="C37" s="14">
+      <c r="C40" s="14">
         <v>90</v>
       </c>
-      <c r="D37" s="14">
+      <c r="D40" s="14">
         <v>180</v>
       </c>
-      <c r="E37" s="14">
+      <c r="E40" s="14">
         <v>120</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F40" s="14">
         <v>250</v>
       </c>
-      <c r="G37" s="14">
+      <c r="G40" s="14">
         <v>5</v>
       </c>
-      <c r="H37" s="14">
+      <c r="H40" s="14">
         <v>90</v>
       </c>
-      <c r="I37" s="15">
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
         <v>1090</v>
       </c>
-      <c r="J37" s="15">
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
         <v>350</v>
       </c>
-      <c r="K37" s="16" t="s">
+      <c r="K40" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L37" s="16" t="s">
+      <c r="L40" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M37" s="16" t="s">
+      <c r="M40" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="N37" s="17" t="s">
+      <c r="N40" s="17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="13">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A41" s="13">
         <v>46281</v>
       </c>
-      <c r="B38" s="14">
+      <c r="B41" s="14">
         <v>360</v>
       </c>
-      <c r="C38" s="14">
+      <c r="C41" s="14">
         <v>120</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D41" s="14">
         <v>120</v>
       </c>
-      <c r="E38" s="14">
+      <c r="E41" s="14">
         <v>50</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F41" s="14">
         <v>250</v>
       </c>
-      <c r="G38" s="14">
+      <c r="G41" s="14">
         <v>5</v>
       </c>
-      <c r="H38" s="14">
+      <c r="H41" s="14">
         <v>180</v>
       </c>
-      <c r="I38" s="15">
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
         <v>1080</v>
       </c>
-      <c r="J38" s="15">
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
         <v>360</v>
       </c>
-      <c r="K38" s="16" t="s">
+      <c r="K41" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L38" s="16" t="s">
+      <c r="L41" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="M38" s="16" t="s">
+      <c r="M41" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N38" s="17" t="s">
+      <c r="N41" s="17" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="13">
-        <v>46282</v>
-      </c>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="13">
-        <v>46283</v>
-      </c>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="13">
-        <v>46284</v>
-      </c>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="13">
-        <v>46285</v>
-      </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+        <v>46282</v>
+      </c>
+      <c r="B42" s="14">
+        <v>300</v>
+      </c>
+      <c r="C42" s="14">
+        <v>90</v>
+      </c>
+      <c r="D42" s="14">
+        <v>90</v>
+      </c>
+      <c r="E42" s="14">
+        <v>50</v>
+      </c>
+      <c r="F42" s="14">
+        <v>300</v>
+      </c>
+      <c r="G42" s="14">
+        <v>6</v>
+      </c>
+      <c r="H42" s="14">
+        <v>120</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="13">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
@@ -2720,7 +2848,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="13">
-        <v>46287</v>
+        <v>46284</v>
       </c>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
@@ -2744,7 +2872,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="13">
-        <v>46288</v>
+        <v>46285</v>
       </c>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
@@ -2767,7 +2895,9 @@
       <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A46" s="13"/>
+      <c r="A46" s="13">
+        <v>46286</v>
+      </c>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
       <c r="D46" s="14"/>
@@ -2789,7 +2919,9 @@
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A47" s="13"/>
+      <c r="A47" s="13">
+        <v>46287</v>
+      </c>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
       <c r="D47" s="14"/>
@@ -2811,7 +2943,9 @@
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A48" s="13"/>
+      <c r="A48" s="13">
+        <v>46288</v>
+      </c>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
@@ -3304,11 +3438,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3326,11 +3460,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3348,11 +3482,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3370,11 +3504,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I73:I136" si="2">IF(SUM(B73:F73,H73)=0,"",SUM(B73:F73,H73))</f>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J73:J136" si="3">IF(I73="","",1440-I73)</f>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -4712,11 +4846,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4734,11 +4868,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4756,11 +4890,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4778,11 +4912,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I137:I200" si="4">IF(SUM(B137:F137,H137)=0,"",SUM(B137:F137,H137))</f>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J137:J200" si="5">IF(I137="","",1440-I137)</f>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -6120,11 +6254,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6142,11 +6276,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6164,11 +6298,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6186,11 +6320,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I201:I264" si="6">IF(SUM(B201:F201,H201)=0,"",SUM(B201:F201,H201))</f>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J201:J264" si="7">IF(I201="","",1440-I201)</f>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -7528,11 +7662,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7550,11 +7684,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7572,11 +7706,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7594,11 +7728,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I265:I328" si="8">IF(SUM(B265:F265,H265)=0,"",SUM(B265:F265,H265))</f>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J265:J328" si="9">IF(I265="","",1440-I265)</f>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -8936,11 +9070,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8958,11 +9092,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8980,11 +9114,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -9002,11 +9136,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I329:I392" si="10">IF(SUM(B329:F329,H329)=0,"",SUM(B329:F329,H329))</f>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J329:J392" si="11">IF(I329="","",1440-I329)</f>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -10344,11 +10478,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10366,11 +10500,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10388,11 +10522,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10410,11 +10544,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I393:I404" si="12">IF(SUM(B393:F393,H393)=0,"",SUM(B393:F393,H393))</f>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J393:J404" si="13">IF(I393="","",1440-I393)</f>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10598,6 +10732,72 @@
       <c r="M401" s="16"/>
       <c r="N401" s="17"/>
     </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A402" s="13"/>
+      <c r="B402" s="14"/>
+      <c r="C402" s="14"/>
+      <c r="D402" s="14"/>
+      <c r="E402" s="14"/>
+      <c r="F402" s="14"/>
+      <c r="G402" s="14"/>
+      <c r="H402" s="14"/>
+      <c r="I402" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J402" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K402" s="16"/>
+      <c r="L402" s="16"/>
+      <c r="M402" s="16"/>
+      <c r="N402" s="17"/>
+    </row>
+    <row r="403" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A403" s="13"/>
+      <c r="B403" s="14"/>
+      <c r="C403" s="14"/>
+      <c r="D403" s="14"/>
+      <c r="E403" s="14"/>
+      <c r="F403" s="14"/>
+      <c r="G403" s="14"/>
+      <c r="H403" s="14"/>
+      <c r="I403" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J403" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K403" s="16"/>
+      <c r="L403" s="16"/>
+      <c r="M403" s="16"/>
+      <c r="N403" s="17"/>
+    </row>
+    <row r="404" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A404" s="13"/>
+      <c r="B404" s="14"/>
+      <c r="C404" s="14"/>
+      <c r="D404" s="14"/>
+      <c r="E404" s="14"/>
+      <c r="F404" s="14"/>
+      <c r="G404" s="14"/>
+      <c r="H404" s="14"/>
+      <c r="I404" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J404" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K404" s="16"/>
+      <c r="L404" s="16"/>
+      <c r="M404" s="16"/>
+      <c r="N404" s="17"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10607,26 +10807,26 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J32 J34:J401">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="J37:J404 J6:J35">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K404">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L404">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M404">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/12625957.xlsx
+++ b/12625957.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -320,6 +320,12 @@
   <si>
     <t xml:space="preserve">start learning coding basic </t>
   </si>
+  <si>
+    <t>SIH hackathon participation</t>
+  </si>
+  <si>
+    <t>woking on project</t>
+  </si>
 </sst>
 </file>
 
@@ -328,7 +334,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -414,6 +420,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -462,7 +474,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -503,9 +515,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -518,22 +527,17 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1011,74 +1015,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="24">
         <v>12625957</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="24"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="24"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
     </row>
     <row r="5" spans="1:14" ht="42" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -1174,45 +1178,45 @@
       <c r="A7" s="13">
         <v>46247</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="25">
         <v>300</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="25">
         <v>50</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="25">
         <v>60</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="19">
         <v>30</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="19">
         <v>250</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="19">
         <v>5</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="19">
         <v>200</v>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="18">
         <f t="shared" si="0"/>
         <v>890</v>
       </c>
-      <c r="J7" s="21">
+      <c r="J7" s="18">
         <f t="shared" si="1"/>
         <v>550</v>
       </c>
-      <c r="K7" s="23" t="s">
+      <c r="K7" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="23" t="s">
+      <c r="L7" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="M7" s="23" t="s">
+      <c r="M7" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="24" t="s">
+      <c r="N7" s="21" t="s">
         <v>93</v>
       </c>
     </row>
@@ -1220,45 +1224,45 @@
       <c r="A8" s="13">
         <v>46248</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="25">
         <v>300</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="25">
         <v>90</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="25">
         <v>90</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="19">
         <v>50</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="19">
         <v>300</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="19">
         <v>6</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="19">
         <v>120</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="18">
         <f t="shared" si="0"/>
         <v>950</v>
       </c>
-      <c r="J8" s="21">
+      <c r="J8" s="18">
         <f t="shared" si="1"/>
         <v>490</v>
       </c>
-      <c r="K8" s="23" t="s">
+      <c r="K8" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="L8" s="23" t="s">
+      <c r="L8" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="M8" s="23" t="s">
+      <c r="M8" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="N8" s="24" t="s">
+      <c r="N8" s="21" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1266,45 +1270,45 @@
       <c r="A9" s="13">
         <v>46249</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="25">
         <v>360</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="25">
         <v>120</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="25">
         <v>60</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="19">
         <v>90</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="19">
         <v>250</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="19">
         <v>5</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="19">
         <v>90</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="18">
         <f t="shared" si="0"/>
         <v>970</v>
       </c>
-      <c r="J9" s="21">
+      <c r="J9" s="18">
         <f t="shared" si="1"/>
         <v>470</v>
       </c>
-      <c r="K9" s="23" t="s">
+      <c r="K9" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="L9" s="23" t="s">
+      <c r="L9" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="M9" s="23" t="s">
+      <c r="M9" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="N9" s="24" t="s">
+      <c r="N9" s="21" t="s">
         <v>95</v>
       </c>
     </row>
@@ -2569,15 +2573,15 @@
         <v>0</v>
       </c>
       <c r="H37" s="14">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v>930</v>
+        <v>970</v>
       </c>
       <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v>510</v>
+        <v>470</v>
       </c>
       <c r="K37" s="16" t="s">
         <v>85</v>
@@ -2799,15 +2803,15 @@
         <v>6</v>
       </c>
       <c r="H42" s="14">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>1070</v>
       </c>
       <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>370</v>
       </c>
       <c r="K42" s="16" t="s">
         <v>58</v>
@@ -2826,73 +2830,139 @@
       <c r="A43" s="13">
         <v>46283</v>
       </c>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="B43" s="14">
+        <v>250</v>
+      </c>
+      <c r="C43" s="14">
+        <v>180</v>
+      </c>
+      <c r="D43" s="14">
+        <v>120</v>
+      </c>
+      <c r="E43" s="14">
+        <v>90</v>
+      </c>
+      <c r="F43" s="14">
+        <v>0</v>
+      </c>
+      <c r="G43" s="14">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14">
+        <v>500</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="13">
         <v>46284</v>
       </c>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="B44" s="14">
+        <v>250</v>
+      </c>
+      <c r="C44" s="14">
+        <v>180</v>
+      </c>
+      <c r="D44" s="14">
+        <v>90</v>
+      </c>
+      <c r="E44" s="14">
+        <v>120</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>500</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="13">
         <v>46285</v>
       </c>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="B45" s="14">
+        <v>400</v>
+      </c>
+      <c r="C45" s="14">
+        <v>90</v>
+      </c>
+      <c r="D45" s="14">
+        <v>180</v>
+      </c>
+      <c r="E45" s="14">
+        <v>60</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>300</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="13">
@@ -10808,7 +10878,7 @@
     <mergeCell ref="F3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="J37:J404 J6:J35">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/12625957.xlsx
+++ b/12625957.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -312,19 +312,16 @@
     <t>practice maths topic percentage</t>
   </si>
   <si>
-    <t>start to add personal data</t>
-  </si>
-  <si>
-    <t>good vibes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">start learning coding basic </t>
-  </si>
-  <si>
     <t>SIH hackathon participation</t>
   </si>
   <si>
     <t>woking on project</t>
+  </si>
+  <si>
+    <t>prepare for python minor project</t>
+  </si>
+  <si>
+    <t>prepare for CA</t>
   </si>
 </sst>
 </file>
@@ -334,7 +331,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -415,17 +412,6 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -474,7 +460,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -515,24 +501,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1000,7 +971,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N404"/>
+  <dimension ref="A1:N400"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1015,74 +986,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="20">
         <v>12625957</v>
       </c>
-      <c r="G2" s="24"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="24"/>
+      <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
     </row>
     <row r="5" spans="1:14" ht="42" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -1154,11 +1125,11 @@
         <v>30</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I72" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I68" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J72" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J68" si="1">IF(I6="","",1440-I6)</f>
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1176,169 +1147,169 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="13">
-        <v>46247</v>
-      </c>
-      <c r="B7" s="25">
-        <v>300</v>
-      </c>
-      <c r="C7" s="25">
+        <v>46250</v>
+      </c>
+      <c r="B7" s="14">
+        <v>480</v>
+      </c>
+      <c r="C7" s="14">
+        <v>120</v>
+      </c>
+      <c r="D7" s="14">
+        <v>180</v>
+      </c>
+      <c r="E7" s="14">
+        <v>180</v>
+      </c>
+      <c r="F7" s="14">
+        <v>0</v>
+      </c>
+      <c r="G7" s="14">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14">
+        <v>120</v>
+      </c>
+      <c r="I7" s="15">
+        <f>IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
+        <v>1080</v>
+      </c>
+      <c r="J7" s="15">
+        <f t="shared" si="1"/>
+        <v>360</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="25">
-        <v>60</v>
-      </c>
-      <c r="E7" s="19">
-        <v>30</v>
-      </c>
-      <c r="F7" s="19">
-        <v>250</v>
-      </c>
-      <c r="G7" s="19">
-        <v>5</v>
-      </c>
-      <c r="H7" s="19">
-        <v>200</v>
-      </c>
-      <c r="I7" s="18">
-        <f t="shared" si="0"/>
-        <v>890</v>
-      </c>
-      <c r="J7" s="18">
-        <f t="shared" si="1"/>
-        <v>550</v>
-      </c>
-      <c r="K7" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="L7" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="M7" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="N7" s="21" t="s">
-        <v>93</v>
+      <c r="M7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="13">
-        <v>46248</v>
-      </c>
-      <c r="B8" s="25">
-        <v>300</v>
-      </c>
-      <c r="C8" s="25">
-        <v>90</v>
-      </c>
-      <c r="D8" s="25">
-        <v>90</v>
-      </c>
-      <c r="E8" s="19">
+        <v>46251</v>
+      </c>
+      <c r="B8" s="14">
+        <v>360</v>
+      </c>
+      <c r="C8" s="14">
+        <v>120</v>
+      </c>
+      <c r="D8" s="14">
+        <v>200</v>
+      </c>
+      <c r="E8" s="14">
+        <v>200</v>
+      </c>
+      <c r="F8" s="14">
+        <v>0</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14">
+        <v>100</v>
+      </c>
+      <c r="I8" s="15">
+        <f t="shared" si="0"/>
+        <v>980</v>
+      </c>
+      <c r="J8" s="15">
+        <f t="shared" si="1"/>
+        <v>460</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="19">
-        <v>300</v>
-      </c>
-      <c r="G8" s="19">
-        <v>6</v>
-      </c>
-      <c r="H8" s="19">
-        <v>120</v>
-      </c>
-      <c r="I8" s="18">
-        <f t="shared" si="0"/>
-        <v>950</v>
-      </c>
-      <c r="J8" s="18">
-        <f t="shared" si="1"/>
-        <v>490</v>
-      </c>
-      <c r="K8" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="L8" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="M8" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="N8" s="21" t="s">
-        <v>94</v>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="13">
-        <v>46249</v>
-      </c>
-      <c r="B9" s="25">
-        <v>360</v>
-      </c>
-      <c r="C9" s="25">
+        <v>46252</v>
+      </c>
+      <c r="B9" s="14">
+        <v>300</v>
+      </c>
+      <c r="C9" s="14">
         <v>120</v>
       </c>
-      <c r="D9" s="25">
-        <v>60</v>
-      </c>
-      <c r="E9" s="19">
-        <v>90</v>
-      </c>
-      <c r="F9" s="19">
-        <v>250</v>
-      </c>
-      <c r="G9" s="19">
-        <v>5</v>
-      </c>
-      <c r="H9" s="19">
-        <v>90</v>
-      </c>
-      <c r="I9" s="18">
+      <c r="D9" s="14">
+        <v>240</v>
+      </c>
+      <c r="E9" s="14">
+        <v>120</v>
+      </c>
+      <c r="F9" s="14">
+        <v>300</v>
+      </c>
+      <c r="G9" s="14">
+        <v>6</v>
+      </c>
+      <c r="H9" s="14">
+        <v>120</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>970</v>
-      </c>
-      <c r="J9" s="18">
+        <v>1200</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>470</v>
-      </c>
-      <c r="K9" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="L9" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="M9" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="N9" s="21" t="s">
-        <v>95</v>
+      <c r="N9" s="17" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="13">
-        <v>46250</v>
+        <v>46253</v>
       </c>
       <c r="B10" s="14">
-        <v>480</v>
+        <v>300</v>
       </c>
       <c r="C10" s="14">
+        <v>70</v>
+      </c>
+      <c r="D10" s="14">
         <v>120</v>
       </c>
-      <c r="D10" s="14">
-        <v>180</v>
-      </c>
       <c r="E10" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="F10" s="14">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="G10" s="14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H10" s="14">
         <v>120</v>
       </c>
       <c r="I10" s="15">
-        <f>IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
+        <f t="shared" si="0"/>
         <v>1080</v>
       </c>
       <c r="J10" s="15">
@@ -1349,18 +1320,18 @@
         <v>49</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="13">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="B11" s="14">
         <v>360</v>
@@ -1369,56 +1340,56 @@
         <v>120</v>
       </c>
       <c r="D11" s="14">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="E11" s="14">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="F11" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G11" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H11" s="14">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>980</v>
+        <v>1200</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>240</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M11" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="13">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="B12" s="14">
         <v>300</v>
       </c>
       <c r="C12" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D12" s="14">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="E12" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="F12" s="14">
         <v>300</v>
@@ -1427,15 +1398,15 @@
         <v>6</v>
       </c>
       <c r="H12" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>1140</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>49</v>
@@ -1444,231 +1415,231 @@
         <v>50</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="13">
-        <v>46253</v>
+        <v>46256</v>
       </c>
       <c r="B13" s="14">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="C13" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D13" s="14">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="E13" s="14">
         <v>120</v>
       </c>
       <c r="F13" s="14">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G13" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H13" s="14">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>1140</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="M13" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="13">
-        <v>46254</v>
+        <v>46257</v>
       </c>
       <c r="B14" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C14" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D14" s="14">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E14" s="14">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="F14" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G14" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H14" s="14">
         <v>180</v>
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>960</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="13">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B15" s="14">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="C15" s="14">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D15" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E15" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="F15" s="14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G15" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H15" s="14">
         <v>180</v>
       </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>1100</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="13">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B16" s="14">
-        <v>420</v>
+        <v>300</v>
       </c>
       <c r="C16" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D16" s="14">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="E16" s="14">
         <v>120</v>
       </c>
       <c r="F16" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G16" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H16" s="14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>1080</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="13">
-        <v>46257</v>
+        <v>46260</v>
       </c>
       <c r="B17" s="14">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="C17" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D17" s="14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E17" s="14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F17" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G17" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H17" s="14">
         <v>180</v>
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1120</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>320</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="L17" s="16" t="s">
         <v>50</v>
@@ -1677,64 +1648,64 @@
         <v>67</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="13">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B18" s="14">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="C18" s="14">
+        <v>90</v>
+      </c>
+      <c r="D18" s="14">
         <v>60</v>
       </c>
-      <c r="D18" s="14">
-        <v>120</v>
-      </c>
       <c r="E18" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F18" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H18" s="14">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>1100</v>
+        <v>1170</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>340</v>
+        <v>270</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="13">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="B19" s="14">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="C19" s="14">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D19" s="14">
         <v>120</v>
@@ -1743,84 +1714,84 @@
         <v>120</v>
       </c>
       <c r="F19" s="14">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G19" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H19" s="14">
-        <v>200</v>
+        <v>360</v>
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>1220</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>220</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="13">
-        <v>46260</v>
+        <v>46263</v>
       </c>
       <c r="B20" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C20" s="14">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D20" s="14">
+        <v>180</v>
+      </c>
+      <c r="E20" s="14">
+        <v>240</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
         <v>120</v>
-      </c>
-      <c r="E20" s="14">
-        <v>120</v>
-      </c>
-      <c r="F20" s="14">
-        <v>250</v>
-      </c>
-      <c r="G20" s="14">
-        <v>5</v>
-      </c>
-      <c r="H20" s="14">
-        <v>180</v>
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>1120</v>
+        <v>1020</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>420</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="L20" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="13">
-        <v>46261</v>
+        <v>46264</v>
       </c>
       <c r="B21" s="14">
         <v>360</v>
@@ -1829,30 +1800,30 @@
         <v>90</v>
       </c>
       <c r="D21" s="14">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="E21" s="14">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F21" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G21" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H21" s="14">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>1170</v>
+        <v>1070</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>270</v>
+        <v>370</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="L21" s="16" t="s">
         <v>65</v>
@@ -1861,41 +1832,41 @@
         <v>71</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="13">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B22" s="14">
         <v>360</v>
       </c>
       <c r="C22" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D22" s="14">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="E22" s="14">
         <v>120</v>
       </c>
       <c r="F22" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H22" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>1220</v>
+        <v>1400</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>40</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>49</v>
@@ -1904,7 +1875,7 @@
         <v>50</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="N22" s="17" t="s">
         <v>62</v>
@@ -1912,36 +1883,36 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="13">
-        <v>46263</v>
+        <v>46266</v>
       </c>
       <c r="B23" s="14">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="C23" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D23" s="14">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="E23" s="14">
         <v>240</v>
       </c>
       <c r="F23" s="14">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="G23" s="14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H23" s="14">
         <v>120</v>
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>1410</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>30</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>49</v>
@@ -1950,7 +1921,7 @@
         <v>50</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="N23" s="17" t="s">
         <v>62</v>
@@ -1958,82 +1929,82 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="13">
-        <v>46264</v>
+        <v>46267</v>
       </c>
       <c r="B24" s="14">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="C24" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D24" s="14">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="E24" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G24" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H24" s="14">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>1070</v>
+        <v>1120</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>370</v>
+        <v>320</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="13">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="B25" s="14">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="C25" s="14">
         <v>120</v>
       </c>
       <c r="D25" s="14">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="E25" s="14">
         <v>120</v>
       </c>
       <c r="F25" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G25" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H25" s="14">
-        <v>300</v>
+        <v>90</v>
       </c>
       <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v>1400</v>
+        <v>1040</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>49</v>
@@ -2042,7 +2013,7 @@
         <v>50</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="N25" s="17" t="s">
         <v>62</v>
@@ -2050,7 +2021,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="13">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="B26" s="14">
         <v>360</v>
@@ -2059,10 +2030,10 @@
         <v>90</v>
       </c>
       <c r="D26" s="14">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="E26" s="14">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="F26" s="14">
         <v>350</v>
@@ -2071,21 +2042,21 @@
         <v>7</v>
       </c>
       <c r="H26" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v>1410</v>
+        <v>1130</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>310</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="M26" s="16" t="s">
         <v>67</v>
@@ -2096,10 +2067,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="13">
-        <v>46267</v>
+        <v>46270</v>
       </c>
       <c r="B27" s="14">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="C27" s="14">
         <v>120</v>
@@ -2108,90 +2079,90 @@
         <v>240</v>
       </c>
       <c r="E27" s="14">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="F27" s="14">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="G27" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>1120</v>
+        <v>1230</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>210</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="13">
-        <v>46268</v>
+        <v>46271</v>
       </c>
       <c r="B28" s="14">
-        <v>370</v>
+        <v>420</v>
       </c>
       <c r="C28" s="14">
         <v>120</v>
       </c>
       <c r="D28" s="14">
-        <v>90</v>
+        <v>300</v>
       </c>
       <c r="E28" s="14">
+        <v>240</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14">
         <v>120</v>
-      </c>
-      <c r="F28" s="14">
-        <v>250</v>
-      </c>
-      <c r="G28" s="14">
-        <v>5</v>
-      </c>
-      <c r="H28" s="14">
-        <v>90</v>
       </c>
       <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v>1040</v>
+        <v>1200</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>240</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="L28" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="13">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B29" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="C29" s="14">
         <v>90</v>
@@ -2203,222 +2174,218 @@
         <v>120</v>
       </c>
       <c r="F29" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G29" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H29" s="14">
         <v>90</v>
       </c>
       <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v>1130</v>
+        <v>1020</v>
       </c>
       <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>420</v>
       </c>
       <c r="K29" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="13">
-        <v>46270</v>
+        <v>46273</v>
       </c>
       <c r="B30" s="14">
-        <v>420</v>
+        <v>300</v>
       </c>
       <c r="C30" s="14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D30" s="14">
         <v>240</v>
       </c>
       <c r="E30" s="14">
-        <v>280</v>
+        <v>120</v>
       </c>
       <c r="F30" s="14">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H30" s="14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v>1230</v>
+        <v>1110</v>
       </c>
       <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" s="13">
-        <v>46271</v>
+        <v>46274</v>
       </c>
       <c r="B31" s="14">
-        <v>420</v>
+        <v>300</v>
       </c>
       <c r="C31" s="14">
+        <v>90</v>
+      </c>
+      <c r="D31" s="14">
+        <v>200</v>
+      </c>
+      <c r="E31" s="14">
         <v>120</v>
       </c>
-      <c r="D31" s="14">
-        <v>300</v>
-      </c>
-      <c r="E31" s="14">
-        <v>240</v>
-      </c>
       <c r="F31" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G31" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H31" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>1050</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>390</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="L31" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M31" s="16" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="13">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="B32" s="14">
         <v>300</v>
       </c>
       <c r="C32" s="14">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="D32" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E32" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F32" s="14">
+        <v>50</v>
+      </c>
+      <c r="G32" s="14">
+        <v>1</v>
+      </c>
+      <c r="H32" s="14">
         <v>300</v>
-      </c>
-      <c r="G32" s="14">
-        <v>6</v>
-      </c>
-      <c r="H32" s="14">
-        <v>90</v>
       </c>
       <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>970</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>470</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="L32" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="13">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="B33" s="14">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="C33" s="14">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="D33" s="14">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="E33" s="14">
         <v>120</v>
       </c>
       <c r="F33" s="14">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="G33" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H33" s="14">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I33" s="15">
-        <f t="shared" si="0"/>
-        <v>1110</v>
-      </c>
-      <c r="J33" s="15">
-        <f t="shared" si="1"/>
-        <v>330</v>
+        <f>IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
+        <v>1210</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="M33" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="13">
-        <v>46274</v>
+        <v>46277</v>
       </c>
       <c r="B34" s="14">
         <v>300</v>
@@ -2427,76 +2394,76 @@
         <v>90</v>
       </c>
       <c r="D34" s="14">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="E34" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F34" s="14">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G34" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H34" s="14">
-        <v>90</v>
+        <v>400</v>
       </c>
       <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>970</v>
       </c>
       <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>470</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="13">
-        <v>46275</v>
+        <v>46278</v>
       </c>
       <c r="B35" s="14">
         <v>300</v>
       </c>
       <c r="C35" s="14">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="D35" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E35" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F35" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G35" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="14">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v>970</v>
+        <v>1020</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v>470</v>
+        <v>420</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="L35" s="16" t="s">
         <v>50</v>
@@ -2505,103 +2472,107 @@
         <v>67</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="13">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B36" s="14">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="C36" s="14">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="D36" s="14">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E36" s="14">
+        <v>60</v>
+      </c>
+      <c r="F36" s="14">
+        <v>200</v>
+      </c>
+      <c r="G36" s="14">
+        <v>4</v>
+      </c>
+      <c r="H36" s="14">
         <v>120</v>
       </c>
-      <c r="F36" s="14">
-        <v>350</v>
-      </c>
-      <c r="G36" s="14">
-        <v>7</v>
-      </c>
-      <c r="H36" s="14">
-        <v>90</v>
-      </c>
       <c r="I36" s="15">
-        <f>IF(SUM(B36:F36,H36)=0,"",SUM(B36:F36,H36))</f>
-        <v>1210</v>
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="J36" s="15">
+        <f t="shared" si="1"/>
+        <v>640</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="L36" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="13">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="B37" s="14">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="C37" s="14">
         <v>90</v>
       </c>
       <c r="D37" s="14">
+        <v>180</v>
+      </c>
+      <c r="E37" s="14">
         <v>120</v>
       </c>
-      <c r="E37" s="14">
-        <v>60</v>
-      </c>
       <c r="F37" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G37" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H37" s="14">
-        <v>400</v>
+        <v>90</v>
       </c>
       <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v>970</v>
+        <v>1090</v>
       </c>
       <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v>470</v>
+        <v>350</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="M37" s="16" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="13">
-        <v>46278</v>
+        <v>46281</v>
       </c>
       <c r="B38" s="14">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="C38" s="14">
         <v>120</v>
@@ -2610,119 +2581,119 @@
         <v>120</v>
       </c>
       <c r="E38" s="14">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="F38" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G38" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H38" s="14">
-        <v>360</v>
+        <v>180</v>
       </c>
       <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>1080</v>
       </c>
       <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="K38" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="M38" s="16" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="13">
-        <v>46279</v>
+        <v>46282</v>
       </c>
       <c r="B39" s="14">
         <v>300</v>
       </c>
       <c r="C39" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D39" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E39" s="14">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F39" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G39" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H39" s="14">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v>800</v>
+        <v>1070</v>
       </c>
       <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v>640</v>
+        <v>370</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="L39" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M39" s="16" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="13">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="B40" s="14">
-        <v>360</v>
+        <v>250</v>
       </c>
       <c r="C40" s="14">
+        <v>180</v>
+      </c>
+      <c r="D40" s="14">
+        <v>120</v>
+      </c>
+      <c r="E40" s="14">
         <v>90</v>
       </c>
-      <c r="D40" s="14">
-        <v>180</v>
-      </c>
-      <c r="E40" s="14">
-        <v>120</v>
-      </c>
       <c r="F40" s="14">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G40" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H40" s="14">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v>1090</v>
+        <v>1140</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="K40" s="16" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="L40" s="16" t="s">
         <v>50</v>
@@ -2731,179 +2702,179 @@
         <v>67</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="13">
-        <v>46281</v>
+        <v>46284</v>
       </c>
       <c r="B41" s="14">
-        <v>360</v>
+        <v>250</v>
       </c>
       <c r="C41" s="14">
+        <v>180</v>
+      </c>
+      <c r="D41" s="14">
+        <v>90</v>
+      </c>
+      <c r="E41" s="14">
         <v>120</v>
       </c>
-      <c r="D41" s="14">
-        <v>120</v>
-      </c>
-      <c r="E41" s="14">
-        <v>50</v>
-      </c>
       <c r="F41" s="14">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G41" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H41" s="14">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>1140</v>
       </c>
       <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="K41" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L41" s="16" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="M41" s="16" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="N41" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="13">
-        <v>46282</v>
+        <v>46285</v>
       </c>
       <c r="B42" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="C42" s="14">
         <v>90</v>
       </c>
       <c r="D42" s="14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E42" s="14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F42" s="14">
+        <v>0</v>
+      </c>
+      <c r="G42" s="14">
+        <v>0</v>
+      </c>
+      <c r="H42" s="14">
         <v>300</v>
-      </c>
-      <c r="G42" s="14">
-        <v>6</v>
-      </c>
-      <c r="H42" s="14">
-        <v>240</v>
       </c>
       <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v>1070</v>
+        <v>1030</v>
       </c>
       <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v>370</v>
+        <v>410</v>
       </c>
       <c r="K42" s="16" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="L42" s="16" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="M42" s="16" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="N42" s="17" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A43" s="13">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B43" s="14">
-        <v>250</v>
+        <v>360</v>
       </c>
       <c r="C43" s="14">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="D43" s="14">
         <v>120</v>
       </c>
       <c r="E43" s="14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="F43" s="14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G43" s="14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H43" s="14">
-        <v>500</v>
+        <v>360</v>
       </c>
       <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>1310</v>
       </c>
       <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>130</v>
       </c>
       <c r="K43" s="16" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L43" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M43" s="16" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="N43" s="17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="13">
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="B44" s="14">
+        <v>300</v>
+      </c>
+      <c r="C44" s="14">
+        <v>100</v>
+      </c>
+      <c r="D44" s="14">
+        <v>120</v>
+      </c>
+      <c r="E44" s="14">
+        <v>180</v>
+      </c>
+      <c r="F44" s="14">
         <v>250</v>
       </c>
-      <c r="C44" s="14">
-        <v>180</v>
-      </c>
-      <c r="D44" s="14">
-        <v>90</v>
-      </c>
-      <c r="E44" s="14">
+      <c r="G44" s="14">
+        <v>5</v>
+      </c>
+      <c r="H44" s="14">
         <v>120</v>
-      </c>
-      <c r="F44" s="14">
-        <v>0</v>
-      </c>
-      <c r="G44" s="14">
-        <v>0</v>
-      </c>
-      <c r="H44" s="14">
-        <v>500</v>
       </c>
       <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>1070</v>
       </c>
       <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>370</v>
       </c>
       <c r="K44" s="16" t="s">
         <v>49</v>
@@ -2912,7 +2883,7 @@
         <v>50</v>
       </c>
       <c r="M44" s="16" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="N44" s="17" t="s">
         <v>96</v>
@@ -2920,54 +2891,30 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="13">
-        <v>46285</v>
-      </c>
-      <c r="B45" s="14">
-        <v>400</v>
-      </c>
-      <c r="C45" s="14">
-        <v>90</v>
-      </c>
-      <c r="D45" s="14">
-        <v>180</v>
-      </c>
-      <c r="E45" s="14">
-        <v>60</v>
-      </c>
-      <c r="F45" s="14">
-        <v>0</v>
-      </c>
-      <c r="G45" s="14">
-        <v>0</v>
-      </c>
-      <c r="H45" s="14">
-        <v>300</v>
-      </c>
-      <c r="I45" s="15">
+        <v>46288</v>
+      </c>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1030</v>
-      </c>
-      <c r="J45" s="15">
+        <v/>
+      </c>
+      <c r="J45" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>410</v>
-      </c>
-      <c r="K45" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="L45" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="M45" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="N45" s="17" t="s">
-        <v>97</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A46" s="13">
-        <v>46286</v>
-      </c>
+      <c r="A46" s="13"/>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
       <c r="D46" s="14"/>
@@ -2989,9 +2936,7 @@
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A47" s="13">
-        <v>46287</v>
-      </c>
+      <c r="A47" s="13"/>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
       <c r="D47" s="14"/>
@@ -3013,9 +2958,7 @@
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A48" s="13">
-        <v>46288</v>
-      </c>
+      <c r="A48" s="13"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
@@ -3486,11 +3429,11 @@
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I69:I132" si="2">IF(SUM(B69:F69,H69)=0,"",SUM(B69:F69,H69))</f>
         <v/>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J69:J132" si="3">IF(I69="","",1440-I69)</f>
         <v/>
       </c>
       <c r="K69" s="16"/>
@@ -3508,11 +3451,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3530,11 +3473,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3552,11 +3495,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3574,11 +3517,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" ref="I73:I136" si="2">IF(SUM(B73:F73,H73)=0,"",SUM(B73:F73,H73))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" ref="J73:J136" si="3">IF(I73="","",1440-I73)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -4894,11 +4837,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I133:I196" si="4">IF(SUM(B133:F133,H133)=0,"",SUM(B133:F133,H133))</f>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J133:J196" si="5">IF(I133="","",1440-I133)</f>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4916,11 +4859,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4938,11 +4881,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4960,11 +4903,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4982,11 +4925,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" ref="I137:I200" si="4">IF(SUM(B137:F137,H137)=0,"",SUM(B137:F137,H137))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" ref="J137:J200" si="5">IF(I137="","",1440-I137)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -6302,11 +6245,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I197:I260" si="6">IF(SUM(B197:F197,H197)=0,"",SUM(B197:F197,H197))</f>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J197:J260" si="7">IF(I197="","",1440-I197)</f>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6324,11 +6267,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6346,11 +6289,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6368,11 +6311,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6390,11 +6333,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" ref="I201:I264" si="6">IF(SUM(B201:F201,H201)=0,"",SUM(B201:F201,H201))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" ref="J201:J264" si="7">IF(I201="","",1440-I201)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -7710,11 +7653,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I261:I324" si="8">IF(SUM(B261:F261,H261)=0,"",SUM(B261:F261,H261))</f>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J261:J324" si="9">IF(I261="","",1440-I261)</f>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7732,11 +7675,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7754,11 +7697,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7776,11 +7719,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7798,11 +7741,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" ref="I265:I328" si="8">IF(SUM(B265:F265,H265)=0,"",SUM(B265:F265,H265))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" ref="J265:J328" si="9">IF(I265="","",1440-I265)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -9118,11 +9061,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I325:I388" si="10">IF(SUM(B325:F325,H325)=0,"",SUM(B325:F325,H325))</f>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J325:J388" si="11">IF(I325="","",1440-I325)</f>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -9140,11 +9083,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -9162,11 +9105,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -9184,11 +9127,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -9206,11 +9149,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" ref="I329:I392" si="10">IF(SUM(B329:F329,H329)=0,"",SUM(B329:F329,H329))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" ref="J329:J392" si="11">IF(I329="","",1440-I329)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -10526,11 +10469,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I389:I400" si="12">IF(SUM(B389:F389,H389)=0,"",SUM(B389:F389,H389))</f>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J389:J400" si="13">IF(I389="","",1440-I389)</f>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10548,11 +10491,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10570,11 +10513,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10592,11 +10535,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10614,11 +10557,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" ref="I393:I404" si="12">IF(SUM(B393:F393,H393)=0,"",SUM(B393:F393,H393))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" ref="J393:J404" si="13">IF(I393="","",1440-I393)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10780,94 +10723,6 @@
       <c r="M400" s="16"/>
       <c r="N400" s="17"/>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A401" s="13"/>
-      <c r="B401" s="14"/>
-      <c r="C401" s="14"/>
-      <c r="D401" s="14"/>
-      <c r="E401" s="14"/>
-      <c r="F401" s="14"/>
-      <c r="G401" s="14"/>
-      <c r="H401" s="14"/>
-      <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K401" s="16"/>
-      <c r="L401" s="16"/>
-      <c r="M401" s="16"/>
-      <c r="N401" s="17"/>
-    </row>
-    <row r="402" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A402" s="13"/>
-      <c r="B402" s="14"/>
-      <c r="C402" s="14"/>
-      <c r="D402" s="14"/>
-      <c r="E402" s="14"/>
-      <c r="F402" s="14"/>
-      <c r="G402" s="14"/>
-      <c r="H402" s="14"/>
-      <c r="I402" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J402" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K402" s="16"/>
-      <c r="L402" s="16"/>
-      <c r="M402" s="16"/>
-      <c r="N402" s="17"/>
-    </row>
-    <row r="403" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A403" s="13"/>
-      <c r="B403" s="14"/>
-      <c r="C403" s="14"/>
-      <c r="D403" s="14"/>
-      <c r="E403" s="14"/>
-      <c r="F403" s="14"/>
-      <c r="G403" s="14"/>
-      <c r="H403" s="14"/>
-      <c r="I403" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J403" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K403" s="16"/>
-      <c r="L403" s="16"/>
-      <c r="M403" s="16"/>
-      <c r="N403" s="17"/>
-    </row>
-    <row r="404" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A404" s="13"/>
-      <c r="B404" s="14"/>
-      <c r="C404" s="14"/>
-      <c r="D404" s="14"/>
-      <c r="E404" s="14"/>
-      <c r="F404" s="14"/>
-      <c r="G404" s="14"/>
-      <c r="H404" s="14"/>
-      <c r="I404" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J404" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K404" s="16"/>
-      <c r="L404" s="16"/>
-      <c r="M404" s="16"/>
-      <c r="N404" s="17"/>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10877,21 +10732,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J37:J404 J6:J35">
+  <conditionalFormatting sqref="J6:J32 J34:J400">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K404">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K400">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L404">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L400">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M404">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M400">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12625957.xlsx
+++ b/12625957.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -322,6 +322,9 @@
   </si>
   <si>
     <t>prepare for CA</t>
+  </si>
+  <si>
+    <t>working on python project</t>
   </si>
 </sst>
 </file>
@@ -2893,28 +2896,52 @@
       <c r="A45" s="13">
         <v>46288</v>
       </c>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="B45" s="14">
+        <v>300</v>
+      </c>
+      <c r="C45" s="14">
+        <v>90</v>
+      </c>
+      <c r="D45" s="14">
+        <v>90</v>
+      </c>
+      <c r="E45" s="14">
+        <v>180</v>
+      </c>
+      <c r="F45" s="14">
+        <v>250</v>
+      </c>
+      <c r="G45" s="14">
+        <v>5</v>
+      </c>
+      <c r="H45" s="14">
+        <v>120</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A46" s="13"/>
+      <c r="A46" s="13">
+        <v>46289</v>
+      </c>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
       <c r="D46" s="14"/>
@@ -2936,7 +2963,9 @@
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A47" s="13"/>
+      <c r="A47" s="13">
+        <v>46290</v>
+      </c>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
       <c r="D47" s="14"/>
@@ -2958,7 +2987,9 @@
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A48" s="13"/>
+      <c r="A48" s="13">
+        <v>46291</v>
+      </c>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
@@ -2980,7 +3011,9 @@
       <c r="N48" s="17"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A49" s="13"/>
+      <c r="A49" s="13">
+        <v>46292</v>
+      </c>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
       <c r="D49" s="14"/>
@@ -3002,7 +3035,9 @@
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A50" s="13"/>
+      <c r="A50" s="13">
+        <v>46293</v>
+      </c>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -3024,7 +3059,9 @@
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A51" s="13"/>
+      <c r="A51" s="13">
+        <v>46294</v>
+      </c>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
       <c r="D51" s="14"/>
@@ -3046,7 +3083,9 @@
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A52" s="13"/>
+      <c r="A52" s="13">
+        <v>46295</v>
+      </c>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
       <c r="D52" s="14"/>

--- a/12625957.xlsx
+++ b/12625957.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -198,22 +198,7 @@
     <t>Tanu Sharma</t>
   </si>
   <si>
-    <t xml:space="preserve">MCA </t>
-  </si>
-  <si>
     <t>August</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>v.Good</t>
-  </si>
-  <si>
-    <t>Normal</t>
-  </si>
-  <si>
-    <t>OK</t>
   </si>
   <si>
     <t>Tired</t>
@@ -222,37 +207,16 @@
     <t>Happy</t>
   </si>
   <si>
-    <t>not Satsfied</t>
-  </si>
-  <si>
     <t>mentally tired</t>
-  </si>
-  <si>
-    <t>not ok</t>
   </si>
   <si>
     <t xml:space="preserve">free day convert into busy day </t>
   </si>
   <si>
-    <t>high</t>
-  </si>
-  <si>
     <t>feel weak</t>
   </si>
   <si>
-    <t>V.Good</t>
-  </si>
-  <si>
-    <t>bit tired</t>
-  </si>
-  <si>
-    <t>low</t>
-  </si>
-  <si>
     <t>feel tense</t>
-  </si>
-  <si>
-    <t>feel low</t>
   </si>
   <si>
     <t>medical issues</t>
@@ -267,13 +231,7 @@
     <t>exhausted</t>
   </si>
   <si>
-    <t>tired</t>
-  </si>
-  <si>
     <t>Neutral</t>
-  </si>
-  <si>
-    <t>Active</t>
   </si>
   <si>
     <t>Worked on database, C++, Python extra codes.</t>
@@ -282,13 +240,7 @@
     <t>Give CA of database sucessfully and parctice for freshers party</t>
   </si>
   <si>
-    <t>Exhauted but happy</t>
-  </si>
-  <si>
     <t xml:space="preserve">todays enjoyed freshers party  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exhauted </t>
   </si>
   <si>
     <t>lil bit hectic</t>
@@ -321,10 +273,34 @@
     <t>prepare for python minor project</t>
   </si>
   <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>MCA /D1P2635</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
     <t>prepare for CA</t>
   </si>
   <si>
     <t>working on python project</t>
+  </si>
+  <si>
+    <t>good day</t>
   </si>
 </sst>
 </file>
@@ -511,7 +487,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1028,7 +1015,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -1036,7 +1023,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1188,10 +1175,10 @@
         <v>50</v>
       </c>
       <c r="M7" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N7" s="17" t="s">
         <v>57</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
@@ -1220,7 +1207,7 @@
         <v>100</v>
       </c>
       <c r="I8" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I8:I47" si="2">IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
         <v>980</v>
       </c>
       <c r="J8" s="15">
@@ -1228,16 +1215,16 @@
         <v>460</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="L8" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
@@ -1266,7 +1253,7 @@
         <v>120</v>
       </c>
       <c r="I9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1200</v>
       </c>
       <c r="J9" s="15">
@@ -1280,10 +1267,10 @@
         <v>50</v>
       </c>
       <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
         <v>57</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
@@ -1312,7 +1299,7 @@
         <v>120</v>
       </c>
       <c r="I10" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1080</v>
       </c>
       <c r="J10" s="15">
@@ -1323,13 +1310,13 @@
         <v>49</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="M10" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
@@ -1358,7 +1345,7 @@
         <v>180</v>
       </c>
       <c r="I11" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1200</v>
       </c>
       <c r="J11" s="15">
@@ -1366,16 +1353,16 @@
         <v>240</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="M11" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -1404,7 +1391,7 @@
         <v>180</v>
       </c>
       <c r="I12" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1140</v>
       </c>
       <c r="J12" s="15">
@@ -1418,10 +1405,10 @@
         <v>50</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
@@ -1450,7 +1437,7 @@
         <v>300</v>
       </c>
       <c r="I13" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1140</v>
       </c>
       <c r="J13" s="15">
@@ -1464,10 +1451,10 @@
         <v>50</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
@@ -1496,7 +1483,7 @@
         <v>180</v>
       </c>
       <c r="I14" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>960</v>
       </c>
       <c r="J14" s="15">
@@ -1504,16 +1491,16 @@
         <v>480</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="L14" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
@@ -1542,7 +1529,7 @@
         <v>180</v>
       </c>
       <c r="I15" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1100</v>
       </c>
       <c r="J15" s="15">
@@ -1553,13 +1540,13 @@
         <v>49</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
@@ -1588,7 +1575,7 @@
         <v>200</v>
       </c>
       <c r="I16" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1080</v>
       </c>
       <c r="J16" s="15">
@@ -1596,16 +1583,16 @@
         <v>360</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
@@ -1634,7 +1621,7 @@
         <v>180</v>
       </c>
       <c r="I17" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1120</v>
       </c>
       <c r="J17" s="15">
@@ -1642,16 +1629,16 @@
         <v>320</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
@@ -1680,7 +1667,7 @@
         <v>300</v>
       </c>
       <c r="I18" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1170</v>
       </c>
       <c r="J18" s="15">
@@ -1688,16 +1675,16 @@
         <v>270</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
@@ -1726,7 +1713,7 @@
         <v>360</v>
       </c>
       <c r="I19" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1220</v>
       </c>
       <c r="J19" s="15">
@@ -1743,7 +1730,7 @@
         <v>51</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
@@ -1772,7 +1759,7 @@
         <v>120</v>
       </c>
       <c r="I20" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1020</v>
       </c>
       <c r="J20" s="15">
@@ -1789,7 +1776,7 @@
         <v>51</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
@@ -1818,7 +1805,7 @@
         <v>240</v>
       </c>
       <c r="I21" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1070</v>
       </c>
       <c r="J21" s="15">
@@ -1826,16 +1813,16 @@
         <v>370</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
@@ -1864,7 +1851,7 @@
         <v>300</v>
       </c>
       <c r="I22" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1400</v>
       </c>
       <c r="J22" s="15">
@@ -1878,10 +1865,10 @@
         <v>50</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
@@ -1910,7 +1897,7 @@
         <v>120</v>
       </c>
       <c r="I23" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1410</v>
       </c>
       <c r="J23" s="15">
@@ -1924,10 +1911,10 @@
         <v>50</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
@@ -1956,7 +1943,7 @@
         <v>60</v>
       </c>
       <c r="I24" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1120</v>
       </c>
       <c r="J24" s="15">
@@ -1964,16 +1951,16 @@
         <v>320</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="M24" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
@@ -2002,7 +1989,7 @@
         <v>90</v>
       </c>
       <c r="I25" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1040</v>
       </c>
       <c r="J25" s="15">
@@ -2019,7 +2006,7 @@
         <v>51</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
@@ -2048,7 +2035,7 @@
         <v>90</v>
       </c>
       <c r="I26" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1130</v>
       </c>
       <c r="J26" s="15">
@@ -2059,13 +2046,13 @@
         <v>49</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
@@ -2094,7 +2081,7 @@
         <v>120</v>
       </c>
       <c r="I27" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1230</v>
       </c>
       <c r="J27" s="15">
@@ -2102,16 +2089,16 @@
         <v>210</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="L27" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
@@ -2140,7 +2127,7 @@
         <v>120</v>
       </c>
       <c r="I28" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1200</v>
       </c>
       <c r="J28" s="15">
@@ -2148,16 +2135,16 @@
         <v>240</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="L28" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
@@ -2186,7 +2173,7 @@
         <v>90</v>
       </c>
       <c r="I29" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1020</v>
       </c>
       <c r="J29" s="15">
@@ -2200,10 +2187,10 @@
         <v>50</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -2232,7 +2219,7 @@
         <v>100</v>
       </c>
       <c r="I30" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1110</v>
       </c>
       <c r="J30" s="15">
@@ -2243,13 +2230,13 @@
         <v>49</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="M30" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -2278,7 +2265,7 @@
         <v>90</v>
       </c>
       <c r="I31" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1050</v>
       </c>
       <c r="J31" s="15">
@@ -2286,19 +2273,19 @@
         <v>390</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="L31" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M31" s="16" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="13">
         <v>46275</v>
       </c>
@@ -2324,7 +2311,7 @@
         <v>300</v>
       </c>
       <c r="I32" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>970</v>
       </c>
       <c r="J32" s="15">
@@ -2332,16 +2319,16 @@
         <v>470</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="L32" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
@@ -2370,11 +2357,15 @@
         <v>90</v>
       </c>
       <c r="I33" s="15">
-        <f>IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
+        <f t="shared" si="2"/>
         <v>1210</v>
       </c>
+      <c r="J33" s="15">
+        <f t="shared" si="1"/>
+        <v>230</v>
+      </c>
       <c r="K33" s="16" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="L33" s="16" t="s">
         <v>50</v>
@@ -2383,7 +2374,7 @@
         <v>51</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
@@ -2412,7 +2403,7 @@
         <v>400</v>
       </c>
       <c r="I34" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>970</v>
       </c>
       <c r="J34" s="15">
@@ -2420,16 +2411,16 @@
         <v>470</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="M34" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
@@ -2458,7 +2449,7 @@
         <v>360</v>
       </c>
       <c r="I35" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1020</v>
       </c>
       <c r="J35" s="15">
@@ -2472,10 +2463,10 @@
         <v>50</v>
       </c>
       <c r="M35" s="16" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
@@ -2504,7 +2495,7 @@
         <v>120</v>
       </c>
       <c r="I36" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>800</v>
       </c>
       <c r="J36" s="15">
@@ -2518,10 +2509,10 @@
         <v>50</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
@@ -2550,7 +2541,7 @@
         <v>90</v>
       </c>
       <c r="I37" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1090</v>
       </c>
       <c r="J37" s="15">
@@ -2564,10 +2555,10 @@
         <v>50</v>
       </c>
       <c r="M37" s="16" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
@@ -2596,7 +2587,7 @@
         <v>180</v>
       </c>
       <c r="I38" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1080</v>
       </c>
       <c r="J38" s="15">
@@ -2607,13 +2598,13 @@
         <v>49</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="M38" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
@@ -2642,7 +2633,7 @@
         <v>240</v>
       </c>
       <c r="I39" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1070</v>
       </c>
       <c r="J39" s="15">
@@ -2650,16 +2641,16 @@
         <v>370</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="L39" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M39" s="16" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
@@ -2688,7 +2679,7 @@
         <v>500</v>
       </c>
       <c r="I40" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1140</v>
       </c>
       <c r="J40" s="15">
@@ -2696,16 +2687,16 @@
         <v>300</v>
       </c>
       <c r="K40" s="16" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="L40" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M40" s="16" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
@@ -2734,7 +2725,7 @@
         <v>500</v>
       </c>
       <c r="I41" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1140</v>
       </c>
       <c r="J41" s="15">
@@ -2748,10 +2739,10 @@
         <v>50</v>
       </c>
       <c r="M41" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="N41" s="17" t="s">
         <v>77</v>
-      </c>
-      <c r="N41" s="17" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
@@ -2780,7 +2771,7 @@
         <v>300</v>
       </c>
       <c r="I42" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1030</v>
       </c>
       <c r="J42" s="15">
@@ -2788,16 +2779,16 @@
         <v>410</v>
       </c>
       <c r="K42" s="16" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L42" s="16" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="M42" s="16" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="N42" s="17" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -2826,7 +2817,7 @@
         <v>360</v>
       </c>
       <c r="I43" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1310</v>
       </c>
       <c r="J43" s="15">
@@ -2843,7 +2834,7 @@
         <v>51</v>
       </c>
       <c r="N43" s="17" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
@@ -2872,7 +2863,7 @@
         <v>120</v>
       </c>
       <c r="I44" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1070</v>
       </c>
       <c r="J44" s="15">
@@ -2886,10 +2877,10 @@
         <v>50</v>
       </c>
       <c r="M44" s="16" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="N44" s="17" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
@@ -2918,7 +2909,7 @@
         <v>120</v>
       </c>
       <c r="I45" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1030</v>
       </c>
       <c r="J45" s="15">
@@ -2935,32 +2926,54 @@
         <v>51</v>
       </c>
       <c r="N45" s="17" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="13">
         <v>46289</v>
       </c>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+      <c r="B46" s="14">
+        <v>360</v>
+      </c>
+      <c r="C46" s="14">
+        <v>90</v>
+      </c>
+      <c r="D46" s="14">
+        <v>90</v>
+      </c>
+      <c r="E46" s="14">
+        <v>120</v>
+      </c>
+      <c r="F46" s="14">
+        <v>300</v>
+      </c>
+      <c r="G46" s="14">
+        <v>6</v>
+      </c>
+      <c r="H46" s="14">
+        <v>180</v>
+      </c>
+      <c r="I46" s="15">
+        <f t="shared" si="2"/>
+        <v>1140</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="13">
@@ -2974,13 +2987,10 @@
       <c r="G47" s="14"/>
       <c r="H47" s="14"/>
       <c r="I47" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J47" s="15"/>
       <c r="K47" s="16"/>
       <c r="L47" s="16"/>
       <c r="M47" s="16"/>
@@ -2997,14 +3007,8 @@
       <c r="F48" s="14"/>
       <c r="G48" s="14"/>
       <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
       <c r="K48" s="16"/>
       <c r="L48" s="16"/>
       <c r="M48" s="16"/>
@@ -3021,14 +3025,8 @@
       <c r="F49" s="14"/>
       <c r="G49" s="14"/>
       <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I49" s="15"/>
+      <c r="J49" s="15"/>
       <c r="K49" s="16"/>
       <c r="L49" s="16"/>
       <c r="M49" s="16"/>
@@ -3045,14 +3043,8 @@
       <c r="F50" s="14"/>
       <c r="G50" s="14"/>
       <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I50" s="15"/>
+      <c r="J50" s="15"/>
       <c r="K50" s="16"/>
       <c r="L50" s="16"/>
       <c r="M50" s="16"/>
@@ -3069,14 +3061,8 @@
       <c r="F51" s="14"/>
       <c r="G51" s="14"/>
       <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I51" s="15"/>
+      <c r="J51" s="15"/>
       <c r="K51" s="16"/>
       <c r="L51" s="16"/>
       <c r="M51" s="16"/>
@@ -3093,21 +3079,17 @@
       <c r="F52" s="14"/>
       <c r="G52" s="14"/>
       <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I52" s="15"/>
+      <c r="J52" s="15"/>
       <c r="K52" s="16"/>
       <c r="L52" s="16"/>
       <c r="M52" s="16"/>
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A53" s="13"/>
+      <c r="A53" s="13">
+        <v>46296</v>
+      </c>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
       <c r="D53" s="14"/>
@@ -3129,7 +3111,9 @@
       <c r="N53" s="17"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A54" s="13"/>
+      <c r="A54" s="13">
+        <v>46297</v>
+      </c>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
       <c r="D54" s="14"/>
@@ -3468,11 +3452,11 @@
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="15" t="str">
-        <f t="shared" ref="I69:I132" si="2">IF(SUM(B69:F69,H69)=0,"",SUM(B69:F69,H69))</f>
+        <f t="shared" ref="I69:I132" si="3">IF(SUM(B69:F69,H69)=0,"",SUM(B69:F69,H69))</f>
         <v/>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" ref="J69:J132" si="3">IF(I69="","",1440-I69)</f>
+        <f t="shared" ref="J69:J132" si="4">IF(I69="","",1440-I69)</f>
         <v/>
       </c>
       <c r="K69" s="16"/>
@@ -3490,11 +3474,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3512,11 +3496,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3534,11 +3518,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3556,11 +3540,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3578,11 +3562,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3600,11 +3584,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3622,11 +3606,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3644,11 +3628,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3666,11 +3650,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3688,11 +3672,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3710,11 +3694,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3732,11 +3716,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3754,11 +3738,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3776,11 +3760,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3798,11 +3782,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3820,11 +3804,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3842,11 +3826,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3864,11 +3848,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3886,11 +3870,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3908,11 +3892,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3930,11 +3914,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3952,11 +3936,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3974,11 +3958,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3996,11 +3980,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -4018,11 +4002,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -4040,11 +4024,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -4062,11 +4046,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -4084,11 +4068,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -4106,11 +4090,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -4128,11 +4112,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -4150,11 +4134,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -4172,11 +4156,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -4194,11 +4178,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -4216,11 +4200,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -4238,11 +4222,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -4260,11 +4244,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -4282,11 +4266,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -4304,11 +4288,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -4326,11 +4310,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -4348,11 +4332,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -4370,11 +4354,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -4392,11 +4376,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -4414,11 +4398,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4436,11 +4420,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4458,11 +4442,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4480,11 +4464,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4502,11 +4486,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4524,11 +4508,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4546,11 +4530,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4568,11 +4552,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4590,11 +4574,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4612,11 +4596,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4634,11 +4618,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4656,11 +4640,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4678,11 +4662,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4700,11 +4684,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4722,11 +4706,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4744,11 +4728,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4766,11 +4750,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4788,11 +4772,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4810,11 +4794,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4832,11 +4816,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4854,11 +4838,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4876,11 +4860,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" ref="I133:I196" si="4">IF(SUM(B133:F133,H133)=0,"",SUM(B133:F133,H133))</f>
+        <f t="shared" ref="I133:I196" si="5">IF(SUM(B133:F133,H133)=0,"",SUM(B133:F133,H133))</f>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" ref="J133:J196" si="5">IF(I133="","",1440-I133)</f>
+        <f t="shared" ref="J133:J196" si="6">IF(I133="","",1440-I133)</f>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4898,11 +4882,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4920,11 +4904,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4942,11 +4926,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4964,11 +4948,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4986,11 +4970,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -5008,11 +4992,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -5030,11 +5014,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -5052,11 +5036,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -5074,11 +5058,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -5096,11 +5080,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -5118,11 +5102,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -5140,11 +5124,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -5162,11 +5146,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -5184,11 +5168,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -5206,11 +5190,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -5228,11 +5212,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -5250,11 +5234,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -5272,11 +5256,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -5294,11 +5278,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -5316,11 +5300,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -5338,11 +5322,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -5360,11 +5344,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -5382,11 +5366,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -5404,11 +5388,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5426,11 +5410,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5448,11 +5432,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5470,11 +5454,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5492,11 +5476,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5514,11 +5498,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5536,11 +5520,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5558,11 +5542,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5580,11 +5564,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5602,11 +5586,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5624,11 +5608,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5646,11 +5630,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5668,11 +5652,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5690,11 +5674,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5712,11 +5696,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5734,11 +5718,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5756,11 +5740,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5778,11 +5762,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5800,11 +5784,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5822,11 +5806,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5844,11 +5828,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5866,11 +5850,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5888,11 +5872,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5910,11 +5894,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5932,11 +5916,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5954,11 +5938,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5976,11 +5960,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5998,11 +5982,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -6020,11 +6004,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -6042,11 +6026,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -6064,11 +6048,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -6086,11 +6070,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -6108,11 +6092,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -6130,11 +6114,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -6152,11 +6136,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -6174,11 +6158,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -6196,11 +6180,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -6218,11 +6202,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -6240,11 +6224,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -6262,11 +6246,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -6284,11 +6268,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" ref="I197:I260" si="6">IF(SUM(B197:F197,H197)=0,"",SUM(B197:F197,H197))</f>
+        <f t="shared" ref="I197:I260" si="7">IF(SUM(B197:F197,H197)=0,"",SUM(B197:F197,H197))</f>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" ref="J197:J260" si="7">IF(I197="","",1440-I197)</f>
+        <f t="shared" ref="J197:J260" si="8">IF(I197="","",1440-I197)</f>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6306,11 +6290,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6328,11 +6312,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6350,11 +6334,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6372,11 +6356,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6394,11 +6378,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -6416,11 +6400,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6438,11 +6422,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -6460,11 +6444,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6482,11 +6466,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6504,11 +6488,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6526,11 +6510,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6548,11 +6532,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6570,11 +6554,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6592,11 +6576,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6614,11 +6598,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6636,11 +6620,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6658,11 +6642,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6680,11 +6664,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6702,11 +6686,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6724,11 +6708,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6746,11 +6730,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6768,11 +6752,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6790,11 +6774,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6812,11 +6796,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6834,11 +6818,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6856,11 +6840,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6878,11 +6862,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6900,11 +6884,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6922,11 +6906,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6944,11 +6928,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6966,11 +6950,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6988,11 +6972,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -7010,11 +6994,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -7032,11 +7016,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -7054,11 +7038,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -7076,11 +7060,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -7098,11 +7082,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -7120,11 +7104,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -7142,11 +7126,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -7164,11 +7148,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -7186,11 +7170,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -7208,11 +7192,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -7230,11 +7214,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -7252,11 +7236,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -7274,11 +7258,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -7296,11 +7280,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -7318,11 +7302,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -7340,11 +7324,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -7362,11 +7346,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -7384,11 +7368,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -7406,11 +7390,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7428,11 +7412,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7450,11 +7434,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7472,11 +7456,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7494,11 +7478,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7516,11 +7500,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7538,11 +7522,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7560,11 +7544,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7582,11 +7566,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7604,11 +7588,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7626,11 +7610,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7648,11 +7632,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7670,11 +7654,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7692,11 +7676,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" ref="I261:I324" si="8">IF(SUM(B261:F261,H261)=0,"",SUM(B261:F261,H261))</f>
+        <f t="shared" ref="I261:I324" si="9">IF(SUM(B261:F261,H261)=0,"",SUM(B261:F261,H261))</f>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" ref="J261:J324" si="9">IF(I261="","",1440-I261)</f>
+        <f t="shared" ref="J261:J324" si="10">IF(I261="","",1440-I261)</f>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7714,11 +7698,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7736,11 +7720,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7758,11 +7742,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7780,11 +7764,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7802,11 +7786,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7824,11 +7808,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7846,11 +7830,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7868,11 +7852,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7890,11 +7874,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7912,11 +7896,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7934,11 +7918,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7956,11 +7940,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7978,11 +7962,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -8000,11 +7984,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -8022,11 +8006,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -8044,11 +8028,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -8066,11 +8050,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -8088,11 +8072,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -8110,11 +8094,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -8132,11 +8116,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -8154,11 +8138,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -8176,11 +8160,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -8198,11 +8182,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -8220,11 +8204,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -8242,11 +8226,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -8264,11 +8248,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -8286,11 +8270,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -8308,11 +8292,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -8330,11 +8314,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -8352,11 +8336,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -8374,11 +8358,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -8396,11 +8380,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -8418,11 +8402,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8440,11 +8424,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8462,11 +8446,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8484,11 +8468,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8506,11 +8490,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8528,11 +8512,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8550,11 +8534,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8572,11 +8556,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8594,11 +8578,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8616,11 +8600,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8638,11 +8622,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8660,11 +8644,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8682,11 +8666,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8704,11 +8688,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8726,11 +8710,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8748,11 +8732,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8770,11 +8754,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8792,11 +8776,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8814,11 +8798,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8836,11 +8820,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8858,11 +8842,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8880,11 +8864,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8902,11 +8886,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8924,11 +8908,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8946,11 +8930,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8968,11 +8952,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8990,11 +8974,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -9012,11 +8996,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -9034,11 +9018,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -9056,11 +9040,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -9078,11 +9062,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -9100,11 +9084,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" ref="I325:I388" si="10">IF(SUM(B325:F325,H325)=0,"",SUM(B325:F325,H325))</f>
+        <f t="shared" ref="I325:I388" si="11">IF(SUM(B325:F325,H325)=0,"",SUM(B325:F325,H325))</f>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" ref="J325:J388" si="11">IF(I325="","",1440-I325)</f>
+        <f t="shared" ref="J325:J388" si="12">IF(I325="","",1440-I325)</f>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -9122,11 +9106,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -9144,11 +9128,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -9166,11 +9150,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -9188,11 +9172,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -9210,11 +9194,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -9232,11 +9216,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -9254,11 +9238,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -9276,11 +9260,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -9298,11 +9282,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -9320,11 +9304,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -9342,11 +9326,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -9364,11 +9348,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -9386,11 +9370,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -9408,11 +9392,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -9430,11 +9414,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9452,11 +9436,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9474,11 +9458,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9496,11 +9480,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9518,11 +9502,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9540,11 +9524,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9562,11 +9546,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9584,11 +9568,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9606,11 +9590,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9628,11 +9612,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9650,11 +9634,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9672,11 +9656,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9694,11 +9678,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9716,11 +9700,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9738,11 +9722,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9760,11 +9744,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9782,11 +9766,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9804,11 +9788,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9826,11 +9810,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9848,11 +9832,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9870,11 +9854,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9892,11 +9876,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9914,11 +9898,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9936,11 +9920,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9958,11 +9942,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9980,11 +9964,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -10002,11 +9986,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -10024,11 +10008,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -10046,11 +10030,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -10068,11 +10052,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -10090,11 +10074,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -10112,11 +10096,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -10134,11 +10118,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -10156,11 +10140,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -10178,11 +10162,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -10200,11 +10184,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -10222,11 +10206,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -10244,11 +10228,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -10266,11 +10250,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -10288,11 +10272,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -10310,11 +10294,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -10332,11 +10316,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -10354,11 +10338,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -10376,11 +10360,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -10398,11 +10382,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -10420,11 +10404,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10442,11 +10426,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10464,11 +10448,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10486,11 +10470,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10508,11 +10492,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" ref="I389:I400" si="12">IF(SUM(B389:F389,H389)=0,"",SUM(B389:F389,H389))</f>
+        <f t="shared" ref="I389:I400" si="13">IF(SUM(B389:F389,H389)=0,"",SUM(B389:F389,H389))</f>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" ref="J389:J400" si="13">IF(I389="","",1440-I389)</f>
+        <f t="shared" ref="J389:J400" si="14">IF(I389="","",1440-I389)</f>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10530,11 +10514,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10552,11 +10536,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10574,11 +10558,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10596,11 +10580,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10618,11 +10602,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10640,11 +10624,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10662,11 +10646,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10684,11 +10668,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10706,11 +10690,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10728,11 +10712,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10750,11 +10734,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10771,8 +10755,8 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J32 J34:J400">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="J6:J400">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/12625957.xlsx
+++ b/12625957.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -301,6 +301,36 @@
   </si>
   <si>
     <t>good day</t>
+  </si>
+  <si>
+    <t>normal day</t>
+  </si>
+  <si>
+    <t>study for exams</t>
+  </si>
+  <si>
+    <t>going home</t>
+  </si>
+  <si>
+    <t>enjoy with family</t>
+  </si>
+  <si>
+    <t>prepare for exams</t>
+  </si>
+  <si>
+    <t>enjoy with frds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">study about self </t>
+  </si>
+  <si>
+    <t>taking online classes</t>
+  </si>
+  <si>
+    <t>enjoy small trip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mock test for preparation </t>
   </si>
 </sst>
 </file>
@@ -1207,7 +1237,7 @@
         <v>100</v>
       </c>
       <c r="I8" s="15">
-        <f t="shared" ref="I8:I47" si="2">IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
+        <f t="shared" ref="I8:I52" si="2">IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
         <v>980</v>
       </c>
       <c r="J8" s="15">
@@ -2979,339 +3009,742 @@
       <c r="A47" s="13">
         <v>46290</v>
       </c>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="B47" s="14">
+        <v>300</v>
+      </c>
+      <c r="C47" s="14">
+        <v>150</v>
+      </c>
+      <c r="D47" s="14">
+        <v>120</v>
+      </c>
+      <c r="E47" s="14">
+        <v>90</v>
+      </c>
+      <c r="F47" s="14">
+        <v>350</v>
+      </c>
+      <c r="G47" s="14">
+        <v>7</v>
+      </c>
+      <c r="H47" s="14">
+        <v>120</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J47" s="15"/>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>1130</v>
+      </c>
+      <c r="J47" s="15">
+        <f t="shared" si="1"/>
+        <v>310</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="13">
         <v>46291</v>
       </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15"/>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+      <c r="B48" s="14">
+        <v>360</v>
+      </c>
+      <c r="C48" s="14">
+        <v>90</v>
+      </c>
+      <c r="D48" s="14">
+        <v>180</v>
+      </c>
+      <c r="E48" s="14">
+        <v>90</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>240</v>
+      </c>
+      <c r="I48" s="15">
+        <f t="shared" si="2"/>
+        <v>960</v>
+      </c>
+      <c r="J48" s="15">
+        <f t="shared" si="1"/>
+        <v>480</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="13">
         <v>46292</v>
       </c>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="15"/>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+      <c r="B49" s="14">
+        <v>400</v>
+      </c>
+      <c r="C49" s="14">
+        <v>120</v>
+      </c>
+      <c r="D49" s="14">
+        <v>60</v>
+      </c>
+      <c r="E49" s="14">
+        <v>60</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>200</v>
+      </c>
+      <c r="I49" s="15">
+        <f t="shared" si="2"/>
+        <v>840</v>
+      </c>
+      <c r="J49" s="15">
+        <f t="shared" si="1"/>
+        <v>600</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="13">
         <v>46293</v>
       </c>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15"/>
-      <c r="J50" s="15"/>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+      <c r="B50" s="14">
+        <v>360</v>
+      </c>
+      <c r="C50" s="14">
+        <v>90</v>
+      </c>
+      <c r="D50" s="14">
+        <v>70</v>
+      </c>
+      <c r="E50" s="14">
+        <v>60</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>240</v>
+      </c>
+      <c r="I50" s="15">
+        <f t="shared" si="2"/>
+        <v>820</v>
+      </c>
+      <c r="J50" s="15">
+        <f t="shared" si="1"/>
+        <v>620</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="13">
         <v>46294</v>
       </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15"/>
-      <c r="J51" s="15"/>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+      <c r="B51" s="14">
+        <v>360</v>
+      </c>
+      <c r="C51" s="14">
+        <v>100</v>
+      </c>
+      <c r="D51" s="14">
+        <v>90</v>
+      </c>
+      <c r="E51" s="14">
+        <v>90</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>200</v>
+      </c>
+      <c r="I51" s="15">
+        <f t="shared" si="2"/>
+        <v>840</v>
+      </c>
+      <c r="J51" s="15">
+        <f t="shared" si="1"/>
+        <v>600</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="13">
         <v>46295</v>
       </c>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15"/>
-      <c r="J52" s="15"/>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+      <c r="B52" s="14">
+        <v>420</v>
+      </c>
+      <c r="C52" s="14">
+        <v>120</v>
+      </c>
+      <c r="D52" s="14">
+        <v>60</v>
+      </c>
+      <c r="E52" s="14">
+        <v>90</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>120</v>
+      </c>
+      <c r="I52" s="15">
+        <f t="shared" si="2"/>
+        <v>810</v>
+      </c>
+      <c r="J52" s="15">
+        <f t="shared" si="1"/>
+        <v>630</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="13">
         <v>46296</v>
       </c>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="B53" s="14">
+        <v>300</v>
+      </c>
+      <c r="C53" s="14">
+        <v>120</v>
+      </c>
+      <c r="D53" s="14">
+        <v>120</v>
+      </c>
+      <c r="E53" s="14">
+        <v>120</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>120</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="13">
         <v>46297</v>
       </c>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="B54" s="14">
+        <v>300</v>
+      </c>
+      <c r="C54" s="14">
+        <v>180</v>
+      </c>
+      <c r="D54" s="14">
+        <v>90</v>
+      </c>
+      <c r="E54" s="14">
+        <v>60</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>90</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B55" s="14">
+        <v>360</v>
+      </c>
+      <c r="C55" s="14">
+        <v>180</v>
+      </c>
+      <c r="D55" s="14">
+        <v>60</v>
+      </c>
+      <c r="E55" s="14">
+        <v>60</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>180</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B56" s="14">
+        <v>360</v>
+      </c>
+      <c r="C56" s="14">
+        <v>180</v>
+      </c>
+      <c r="D56" s="14">
+        <v>90</v>
+      </c>
+      <c r="E56" s="14">
+        <v>60</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>180</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B57" s="14">
+        <v>300</v>
+      </c>
+      <c r="C57" s="14">
+        <v>120</v>
+      </c>
+      <c r="D57" s="14">
+        <v>120</v>
+      </c>
+      <c r="E57" s="14">
+        <v>120</v>
+      </c>
+      <c r="F57" s="14">
+        <v>100</v>
+      </c>
+      <c r="G57" s="14">
+        <v>2</v>
+      </c>
+      <c r="H57" s="14">
+        <v>120</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B58" s="14">
+        <v>240</v>
+      </c>
+      <c r="C58" s="14">
+        <v>90</v>
+      </c>
+      <c r="D58" s="14">
+        <v>180</v>
+      </c>
+      <c r="E58" s="14">
+        <v>120</v>
+      </c>
+      <c r="F58" s="14">
+        <v>200</v>
+      </c>
+      <c r="G58" s="14">
+        <v>4</v>
+      </c>
+      <c r="H58" s="14">
+        <v>120</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B59" s="14">
+        <v>300</v>
+      </c>
+      <c r="C59" s="14">
+        <v>90</v>
+      </c>
+      <c r="D59" s="14">
+        <v>200</v>
+      </c>
+      <c r="E59" s="14">
+        <v>90</v>
+      </c>
+      <c r="F59" s="14">
+        <v>150</v>
+      </c>
+      <c r="G59" s="14">
+        <v>3</v>
+      </c>
+      <c r="H59" s="14">
+        <v>240</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B60" s="14">
+        <v>420</v>
+      </c>
+      <c r="C60" s="14">
+        <v>90</v>
+      </c>
+      <c r="D60" s="14">
+        <v>200</v>
+      </c>
+      <c r="E60" s="14">
+        <v>90</v>
+      </c>
+      <c r="F60" s="14">
+        <v>100</v>
+      </c>
+      <c r="G60" s="14">
+        <v>2</v>
+      </c>
+      <c r="H60" s="14">
+        <v>180</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B61" s="14">
+        <v>360</v>
+      </c>
+      <c r="C61" s="14">
+        <v>120</v>
+      </c>
+      <c r="D61" s="14">
+        <v>240</v>
+      </c>
+      <c r="E61" s="14">
+        <v>120</v>
+      </c>
+      <c r="F61" s="14">
+        <v>50</v>
+      </c>
+      <c r="G61" s="14">
+        <v>1</v>
+      </c>
+      <c r="H61" s="14">
+        <v>180</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B62" s="14">
+        <v>300</v>
+      </c>
+      <c r="C62" s="14">
+        <v>90</v>
+      </c>
+      <c r="D62" s="14">
+        <v>300</v>
+      </c>
+      <c r="E62" s="14">
+        <v>60</v>
+      </c>
+      <c r="F62" s="14">
+        <v>0</v>
+      </c>
+      <c r="G62" s="14">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14">
+        <v>200</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A63" s="13"/>
+      <c r="A63" s="13">
+        <v>46306</v>
+      </c>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
       <c r="D63" s="14"/>
@@ -3333,7 +3766,9 @@
       <c r="N63" s="17"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A64" s="13"/>
+      <c r="A64" s="13">
+        <v>46307</v>
+      </c>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
       <c r="D64" s="14"/>
@@ -3355,7 +3790,9 @@
       <c r="N64" s="17"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A65" s="13"/>
+      <c r="A65" s="13">
+        <v>46308</v>
+      </c>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
@@ -3377,7 +3814,9 @@
       <c r="N65" s="17"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A66" s="13"/>
+      <c r="A66" s="13">
+        <v>46309</v>
+      </c>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
       <c r="D66" s="14"/>
@@ -3399,7 +3838,9 @@
       <c r="N66" s="17"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A67" s="13"/>
+      <c r="A67" s="13">
+        <v>46310</v>
+      </c>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
       <c r="D67" s="14"/>
@@ -3421,7 +3862,9 @@
       <c r="N67" s="17"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A68" s="13"/>
+      <c r="A68" s="13">
+        <v>46311</v>
+      </c>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
       <c r="D68" s="14"/>
@@ -3443,7 +3886,9 @@
       <c r="N68" s="17"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A69" s="13"/>
+      <c r="A69" s="13">
+        <v>46312</v>
+      </c>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
       <c r="D69" s="14"/>
@@ -3465,7 +3910,9 @@
       <c r="N69" s="17"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A70" s="13"/>
+      <c r="A70" s="13">
+        <v>46313</v>
+      </c>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -3487,7 +3934,9 @@
       <c r="N70" s="17"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A71" s="13"/>
+      <c r="A71" s="13">
+        <v>46314</v>
+      </c>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
       <c r="D71" s="14"/>
@@ -3509,7 +3958,9 @@
       <c r="N71" s="17"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A72" s="13"/>
+      <c r="A72" s="13">
+        <v>46315</v>
+      </c>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
       <c r="D72" s="14"/>
@@ -3531,7 +3982,9 @@
       <c r="N72" s="17"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A73" s="13"/>
+      <c r="A73" s="13">
+        <v>46316</v>
+      </c>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
       <c r="D73" s="14"/>
@@ -3553,7 +4006,9 @@
       <c r="N73" s="17"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A74" s="13"/>
+      <c r="A74" s="13">
+        <v>46317</v>
+      </c>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -3575,7 +4030,9 @@
       <c r="N74" s="17"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A75" s="13"/>
+      <c r="A75" s="13">
+        <v>46318</v>
+      </c>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
       <c r="D75" s="14"/>
@@ -3597,7 +4054,9 @@
       <c r="N75" s="17"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A76" s="13"/>
+      <c r="A76" s="13">
+        <v>46319</v>
+      </c>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
       <c r="D76" s="14"/>
@@ -3619,7 +4078,9 @@
       <c r="N76" s="17"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A77" s="13"/>
+      <c r="A77" s="13">
+        <v>46320</v>
+      </c>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
       <c r="D77" s="14"/>
@@ -3641,7 +4102,9 @@
       <c r="N77" s="17"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A78" s="13"/>
+      <c r="A78" s="13">
+        <v>46321</v>
+      </c>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
       <c r="D78" s="14"/>
@@ -3663,7 +4126,9 @@
       <c r="N78" s="17"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A79" s="13"/>
+      <c r="A79" s="13">
+        <v>46322</v>
+      </c>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
       <c r="D79" s="14"/>
@@ -3685,7 +4150,9 @@
       <c r="N79" s="17"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A80" s="13"/>
+      <c r="A80" s="13">
+        <v>46323</v>
+      </c>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
       <c r="D80" s="14"/>
@@ -3707,7 +4174,9 @@
       <c r="N80" s="17"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A81" s="13"/>
+      <c r="A81" s="13">
+        <v>46324</v>
+      </c>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
       <c r="D81" s="14"/>
@@ -3729,7 +4198,9 @@
       <c r="N81" s="17"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A82" s="13"/>
+      <c r="A82" s="13">
+        <v>46325</v>
+      </c>
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
       <c r="D82" s="14"/>
@@ -3751,7 +4222,9 @@
       <c r="N82" s="17"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A83" s="13"/>
+      <c r="A83" s="13">
+        <v>46326</v>
+      </c>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
       <c r="D83" s="14"/>

--- a/12625957.xlsx
+++ b/12625957.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -332,6 +332,12 @@
   <si>
     <t xml:space="preserve">mock test for preparation </t>
   </si>
+  <si>
+    <t>prepare for Networking exam</t>
+  </si>
+  <si>
+    <t>Go to outside</t>
+  </si>
 </sst>
 </file>
 
@@ -517,18 +523,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3745,121 +3740,231 @@
       <c r="A63" s="13">
         <v>46306</v>
       </c>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="B63" s="14">
+        <v>300</v>
+      </c>
+      <c r="C63" s="14">
+        <v>120</v>
+      </c>
+      <c r="D63" s="14">
+        <v>300</v>
+      </c>
+      <c r="E63" s="14">
+        <v>90</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>100</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="13">
         <v>46307</v>
       </c>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="B64" s="14">
+        <v>360</v>
+      </c>
+      <c r="C64" s="14">
+        <v>90</v>
+      </c>
+      <c r="D64" s="14">
+        <v>240</v>
+      </c>
+      <c r="E64" s="14">
+        <v>60</v>
+      </c>
+      <c r="F64" s="14">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>200</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="13">
         <v>46308</v>
       </c>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="B65" s="14">
+        <v>360</v>
+      </c>
+      <c r="C65" s="14">
+        <v>90</v>
+      </c>
+      <c r="D65" s="14">
+        <v>200</v>
+      </c>
+      <c r="E65" s="14">
+        <v>100</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>180</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="13">
         <v>46309</v>
       </c>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+      <c r="B66" s="14">
+        <v>360</v>
+      </c>
+      <c r="C66" s="14">
+        <v>120</v>
+      </c>
+      <c r="D66" s="14">
+        <v>280</v>
+      </c>
+      <c r="E66" s="14">
+        <v>90</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>90</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="13">
         <v>46310</v>
       </c>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+      <c r="B67" s="14">
+        <v>420</v>
+      </c>
+      <c r="C67" s="14">
+        <v>180</v>
+      </c>
+      <c r="D67" s="14">
+        <v>180</v>
+      </c>
+      <c r="E67" s="14">
+        <v>90</v>
+      </c>
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>90</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N67" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="13">
@@ -11229,7 +11334,7 @@
     <mergeCell ref="F3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="J6:J400">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
